--- a/data/gafor_log.xlsx
+++ b/data/gafor_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CG173"/>
+  <dimension ref="A1:CG174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23375,6 +23375,137 @@
       <c r="CF173" t="inlineStr"/>
       <c r="CG173" t="inlineStr"/>
     </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2026-09-07 08:00</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Ostfriesland</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Nordfriesland-Dithmarschen</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Schleswig-Holsteinische Geest</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Schleswig-Holsteinisches Hügelland</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>Nordwestliches Niedersachsen</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>Lüneburger Heide</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Westliches Niedersachsen</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>Hannover und Braunschweig</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>Teutoburger Wald</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Weser-Leine-Bergland</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr"/>
+      <c r="M174" t="inlineStr"/>
+      <c r="N174" t="inlineStr"/>
+      <c r="O174" t="inlineStr"/>
+      <c r="P174" t="inlineStr"/>
+      <c r="Q174" t="inlineStr"/>
+      <c r="R174" t="inlineStr"/>
+      <c r="S174" t="inlineStr"/>
+      <c r="T174" t="inlineStr"/>
+      <c r="U174" t="inlineStr"/>
+      <c r="V174" t="inlineStr"/>
+      <c r="W174" t="inlineStr"/>
+      <c r="X174" t="inlineStr"/>
+      <c r="Y174" t="inlineStr"/>
+      <c r="Z174" t="inlineStr"/>
+      <c r="AA174" t="inlineStr"/>
+      <c r="AB174" t="inlineStr"/>
+      <c r="AC174" t="inlineStr"/>
+      <c r="AD174" t="inlineStr"/>
+      <c r="AE174" t="inlineStr"/>
+      <c r="AF174" t="inlineStr"/>
+      <c r="AG174" t="inlineStr"/>
+      <c r="AH174" t="inlineStr"/>
+      <c r="AI174" t="inlineStr"/>
+      <c r="AJ174" t="inlineStr"/>
+      <c r="AK174" t="inlineStr"/>
+      <c r="AL174" t="inlineStr"/>
+      <c r="AM174" t="inlineStr"/>
+      <c r="AN174" t="inlineStr"/>
+      <c r="AO174" t="inlineStr"/>
+      <c r="AP174" t="inlineStr"/>
+      <c r="AQ174" t="inlineStr"/>
+      <c r="AR174" t="inlineStr"/>
+      <c r="AS174" t="inlineStr"/>
+      <c r="AT174" t="inlineStr"/>
+      <c r="AU174" t="inlineStr"/>
+      <c r="AV174" t="inlineStr"/>
+      <c r="AW174" t="inlineStr"/>
+      <c r="AX174" t="inlineStr"/>
+      <c r="AY174" t="inlineStr"/>
+      <c r="AZ174" t="inlineStr"/>
+      <c r="BA174" t="inlineStr"/>
+      <c r="BB174" t="inlineStr"/>
+      <c r="BC174" t="inlineStr"/>
+      <c r="BD174" t="inlineStr"/>
+      <c r="BE174" t="inlineStr"/>
+      <c r="BF174" t="inlineStr"/>
+      <c r="BG174" t="inlineStr"/>
+      <c r="BH174" t="inlineStr"/>
+      <c r="BI174" t="inlineStr"/>
+      <c r="BJ174" t="inlineStr"/>
+      <c r="BK174" t="inlineStr"/>
+      <c r="BL174" t="inlineStr"/>
+      <c r="BM174" t="inlineStr"/>
+      <c r="BN174" t="inlineStr"/>
+      <c r="BO174" t="inlineStr"/>
+      <c r="BP174" t="inlineStr"/>
+      <c r="BQ174" t="inlineStr"/>
+      <c r="BR174" t="inlineStr"/>
+      <c r="BS174" t="inlineStr"/>
+      <c r="BT174" t="inlineStr"/>
+      <c r="BU174" t="inlineStr"/>
+      <c r="BV174" t="inlineStr"/>
+      <c r="BW174" t="inlineStr"/>
+      <c r="BX174" t="inlineStr"/>
+      <c r="BY174" t="inlineStr"/>
+      <c r="BZ174" t="inlineStr"/>
+      <c r="CA174" t="inlineStr"/>
+      <c r="CB174" t="inlineStr"/>
+      <c r="CC174" t="inlineStr"/>
+      <c r="CD174" t="inlineStr"/>
+      <c r="CE174" t="inlineStr"/>
+      <c r="CF174" t="inlineStr"/>
+      <c r="CG174" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gafor_log.xlsx
+++ b/data/gafor_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CG174"/>
+  <dimension ref="A1:CG175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23506,6 +23506,137 @@
       <c r="CF174" t="inlineStr"/>
       <c r="CG174" t="inlineStr"/>
     </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2026-09-08 08:00</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Ostfriesland</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Nordfriesland-Dithmarschen</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Schleswig-Holsteinische Geest</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Schleswig-Holsteinisches Hügelland</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>Nordwestliches Niedersachsen</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>Lüneburger Heide</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Westliches Niedersachsen</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>Hannover und Braunschweig</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>Teutoburger Wald</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Weser-Leine-Bergland</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr"/>
+      <c r="M175" t="inlineStr"/>
+      <c r="N175" t="inlineStr"/>
+      <c r="O175" t="inlineStr"/>
+      <c r="P175" t="inlineStr"/>
+      <c r="Q175" t="inlineStr"/>
+      <c r="R175" t="inlineStr"/>
+      <c r="S175" t="inlineStr"/>
+      <c r="T175" t="inlineStr"/>
+      <c r="U175" t="inlineStr"/>
+      <c r="V175" t="inlineStr"/>
+      <c r="W175" t="inlineStr"/>
+      <c r="X175" t="inlineStr"/>
+      <c r="Y175" t="inlineStr"/>
+      <c r="Z175" t="inlineStr"/>
+      <c r="AA175" t="inlineStr"/>
+      <c r="AB175" t="inlineStr"/>
+      <c r="AC175" t="inlineStr"/>
+      <c r="AD175" t="inlineStr"/>
+      <c r="AE175" t="inlineStr"/>
+      <c r="AF175" t="inlineStr"/>
+      <c r="AG175" t="inlineStr"/>
+      <c r="AH175" t="inlineStr"/>
+      <c r="AI175" t="inlineStr"/>
+      <c r="AJ175" t="inlineStr"/>
+      <c r="AK175" t="inlineStr"/>
+      <c r="AL175" t="inlineStr"/>
+      <c r="AM175" t="inlineStr"/>
+      <c r="AN175" t="inlineStr"/>
+      <c r="AO175" t="inlineStr"/>
+      <c r="AP175" t="inlineStr"/>
+      <c r="AQ175" t="inlineStr"/>
+      <c r="AR175" t="inlineStr"/>
+      <c r="AS175" t="inlineStr"/>
+      <c r="AT175" t="inlineStr"/>
+      <c r="AU175" t="inlineStr"/>
+      <c r="AV175" t="inlineStr"/>
+      <c r="AW175" t="inlineStr"/>
+      <c r="AX175" t="inlineStr"/>
+      <c r="AY175" t="inlineStr"/>
+      <c r="AZ175" t="inlineStr"/>
+      <c r="BA175" t="inlineStr"/>
+      <c r="BB175" t="inlineStr"/>
+      <c r="BC175" t="inlineStr"/>
+      <c r="BD175" t="inlineStr"/>
+      <c r="BE175" t="inlineStr"/>
+      <c r="BF175" t="inlineStr"/>
+      <c r="BG175" t="inlineStr"/>
+      <c r="BH175" t="inlineStr"/>
+      <c r="BI175" t="inlineStr"/>
+      <c r="BJ175" t="inlineStr"/>
+      <c r="BK175" t="inlineStr"/>
+      <c r="BL175" t="inlineStr"/>
+      <c r="BM175" t="inlineStr"/>
+      <c r="BN175" t="inlineStr"/>
+      <c r="BO175" t="inlineStr"/>
+      <c r="BP175" t="inlineStr"/>
+      <c r="BQ175" t="inlineStr"/>
+      <c r="BR175" t="inlineStr"/>
+      <c r="BS175" t="inlineStr"/>
+      <c r="BT175" t="inlineStr"/>
+      <c r="BU175" t="inlineStr"/>
+      <c r="BV175" t="inlineStr"/>
+      <c r="BW175" t="inlineStr"/>
+      <c r="BX175" t="inlineStr"/>
+      <c r="BY175" t="inlineStr"/>
+      <c r="BZ175" t="inlineStr"/>
+      <c r="CA175" t="inlineStr"/>
+      <c r="CB175" t="inlineStr"/>
+      <c r="CC175" t="inlineStr"/>
+      <c r="CD175" t="inlineStr"/>
+      <c r="CE175" t="inlineStr"/>
+      <c r="CF175" t="inlineStr"/>
+      <c r="CG175" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gafor_log.xlsx
+++ b/data/gafor_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CG175"/>
+  <dimension ref="A1:CG176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23637,6 +23637,137 @@
       <c r="CF175" t="inlineStr"/>
       <c r="CG175" t="inlineStr"/>
     </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2026-09-09 08:00</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Ostfriesland</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Nordfriesland-Dithmarschen</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Schleswig-Holsteinische Geest</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Schleswig-Holsteinisches Hügelland</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>Nordwestliches Niedersachsen</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>Lüneburger Heide</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Westliches Niedersachsen</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>Hannover und Braunschweig</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>Teutoburger Wald</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Weser-Leine-Bergland</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr"/>
+      <c r="M176" t="inlineStr"/>
+      <c r="N176" t="inlineStr"/>
+      <c r="O176" t="inlineStr"/>
+      <c r="P176" t="inlineStr"/>
+      <c r="Q176" t="inlineStr"/>
+      <c r="R176" t="inlineStr"/>
+      <c r="S176" t="inlineStr"/>
+      <c r="T176" t="inlineStr"/>
+      <c r="U176" t="inlineStr"/>
+      <c r="V176" t="inlineStr"/>
+      <c r="W176" t="inlineStr"/>
+      <c r="X176" t="inlineStr"/>
+      <c r="Y176" t="inlineStr"/>
+      <c r="Z176" t="inlineStr"/>
+      <c r="AA176" t="inlineStr"/>
+      <c r="AB176" t="inlineStr"/>
+      <c r="AC176" t="inlineStr"/>
+      <c r="AD176" t="inlineStr"/>
+      <c r="AE176" t="inlineStr"/>
+      <c r="AF176" t="inlineStr"/>
+      <c r="AG176" t="inlineStr"/>
+      <c r="AH176" t="inlineStr"/>
+      <c r="AI176" t="inlineStr"/>
+      <c r="AJ176" t="inlineStr"/>
+      <c r="AK176" t="inlineStr"/>
+      <c r="AL176" t="inlineStr"/>
+      <c r="AM176" t="inlineStr"/>
+      <c r="AN176" t="inlineStr"/>
+      <c r="AO176" t="inlineStr"/>
+      <c r="AP176" t="inlineStr"/>
+      <c r="AQ176" t="inlineStr"/>
+      <c r="AR176" t="inlineStr"/>
+      <c r="AS176" t="inlineStr"/>
+      <c r="AT176" t="inlineStr"/>
+      <c r="AU176" t="inlineStr"/>
+      <c r="AV176" t="inlineStr"/>
+      <c r="AW176" t="inlineStr"/>
+      <c r="AX176" t="inlineStr"/>
+      <c r="AY176" t="inlineStr"/>
+      <c r="AZ176" t="inlineStr"/>
+      <c r="BA176" t="inlineStr"/>
+      <c r="BB176" t="inlineStr"/>
+      <c r="BC176" t="inlineStr"/>
+      <c r="BD176" t="inlineStr"/>
+      <c r="BE176" t="inlineStr"/>
+      <c r="BF176" t="inlineStr"/>
+      <c r="BG176" t="inlineStr"/>
+      <c r="BH176" t="inlineStr"/>
+      <c r="BI176" t="inlineStr"/>
+      <c r="BJ176" t="inlineStr"/>
+      <c r="BK176" t="inlineStr"/>
+      <c r="BL176" t="inlineStr"/>
+      <c r="BM176" t="inlineStr"/>
+      <c r="BN176" t="inlineStr"/>
+      <c r="BO176" t="inlineStr"/>
+      <c r="BP176" t="inlineStr"/>
+      <c r="BQ176" t="inlineStr"/>
+      <c r="BR176" t="inlineStr"/>
+      <c r="BS176" t="inlineStr"/>
+      <c r="BT176" t="inlineStr"/>
+      <c r="BU176" t="inlineStr"/>
+      <c r="BV176" t="inlineStr"/>
+      <c r="BW176" t="inlineStr"/>
+      <c r="BX176" t="inlineStr"/>
+      <c r="BY176" t="inlineStr"/>
+      <c r="BZ176" t="inlineStr"/>
+      <c r="CA176" t="inlineStr"/>
+      <c r="CB176" t="inlineStr"/>
+      <c r="CC176" t="inlineStr"/>
+      <c r="CD176" t="inlineStr"/>
+      <c r="CE176" t="inlineStr"/>
+      <c r="CF176" t="inlineStr"/>
+      <c r="CG176" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gafor_log.xlsx
+++ b/data/gafor_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CG176"/>
+  <dimension ref="A1:CG177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23768,6 +23768,137 @@
       <c r="CF176" t="inlineStr"/>
       <c r="CG176" t="inlineStr"/>
     </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2026-09-10 08:00</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Ostfriesland</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Nordfriesland-Dithmarschen</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Schleswig-Holsteinische Geest</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Schleswig-Holsteinisches Hügelland</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>Nordwestliches Niedersachsen</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>Lüneburger Heide</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Westliches Niedersachsen</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>Hannover und Braunschweig</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>Teutoburger Wald</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Weser-Leine-Bergland</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr"/>
+      <c r="M177" t="inlineStr"/>
+      <c r="N177" t="inlineStr"/>
+      <c r="O177" t="inlineStr"/>
+      <c r="P177" t="inlineStr"/>
+      <c r="Q177" t="inlineStr"/>
+      <c r="R177" t="inlineStr"/>
+      <c r="S177" t="inlineStr"/>
+      <c r="T177" t="inlineStr"/>
+      <c r="U177" t="inlineStr"/>
+      <c r="V177" t="inlineStr"/>
+      <c r="W177" t="inlineStr"/>
+      <c r="X177" t="inlineStr"/>
+      <c r="Y177" t="inlineStr"/>
+      <c r="Z177" t="inlineStr"/>
+      <c r="AA177" t="inlineStr"/>
+      <c r="AB177" t="inlineStr"/>
+      <c r="AC177" t="inlineStr"/>
+      <c r="AD177" t="inlineStr"/>
+      <c r="AE177" t="inlineStr"/>
+      <c r="AF177" t="inlineStr"/>
+      <c r="AG177" t="inlineStr"/>
+      <c r="AH177" t="inlineStr"/>
+      <c r="AI177" t="inlineStr"/>
+      <c r="AJ177" t="inlineStr"/>
+      <c r="AK177" t="inlineStr"/>
+      <c r="AL177" t="inlineStr"/>
+      <c r="AM177" t="inlineStr"/>
+      <c r="AN177" t="inlineStr"/>
+      <c r="AO177" t="inlineStr"/>
+      <c r="AP177" t="inlineStr"/>
+      <c r="AQ177" t="inlineStr"/>
+      <c r="AR177" t="inlineStr"/>
+      <c r="AS177" t="inlineStr"/>
+      <c r="AT177" t="inlineStr"/>
+      <c r="AU177" t="inlineStr"/>
+      <c r="AV177" t="inlineStr"/>
+      <c r="AW177" t="inlineStr"/>
+      <c r="AX177" t="inlineStr"/>
+      <c r="AY177" t="inlineStr"/>
+      <c r="AZ177" t="inlineStr"/>
+      <c r="BA177" t="inlineStr"/>
+      <c r="BB177" t="inlineStr"/>
+      <c r="BC177" t="inlineStr"/>
+      <c r="BD177" t="inlineStr"/>
+      <c r="BE177" t="inlineStr"/>
+      <c r="BF177" t="inlineStr"/>
+      <c r="BG177" t="inlineStr"/>
+      <c r="BH177" t="inlineStr"/>
+      <c r="BI177" t="inlineStr"/>
+      <c r="BJ177" t="inlineStr"/>
+      <c r="BK177" t="inlineStr"/>
+      <c r="BL177" t="inlineStr"/>
+      <c r="BM177" t="inlineStr"/>
+      <c r="BN177" t="inlineStr"/>
+      <c r="BO177" t="inlineStr"/>
+      <c r="BP177" t="inlineStr"/>
+      <c r="BQ177" t="inlineStr"/>
+      <c r="BR177" t="inlineStr"/>
+      <c r="BS177" t="inlineStr"/>
+      <c r="BT177" t="inlineStr"/>
+      <c r="BU177" t="inlineStr"/>
+      <c r="BV177" t="inlineStr"/>
+      <c r="BW177" t="inlineStr"/>
+      <c r="BX177" t="inlineStr"/>
+      <c r="BY177" t="inlineStr"/>
+      <c r="BZ177" t="inlineStr"/>
+      <c r="CA177" t="inlineStr"/>
+      <c r="CB177" t="inlineStr"/>
+      <c r="CC177" t="inlineStr"/>
+      <c r="CD177" t="inlineStr"/>
+      <c r="CE177" t="inlineStr"/>
+      <c r="CF177" t="inlineStr"/>
+      <c r="CG177" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gafor_log.xlsx
+++ b/data/gafor_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CG177"/>
+  <dimension ref="A1:CG178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23899,6 +23899,137 @@
       <c r="CF177" t="inlineStr"/>
       <c r="CG177" t="inlineStr"/>
     </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2026-09-11 08:00</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Ostfriesland</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Nordfriesland-Dithmarschen</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Schleswig-Holsteinische Geest</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Schleswig-Holsteinisches Hügelland</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Nordwestliches Niedersachsen</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>Lüneburger Heide</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Westliches Niedersachsen</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>Hannover und Braunschweig</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>Teutoburger Wald</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Weser-Leine-Bergland</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr"/>
+      <c r="M178" t="inlineStr"/>
+      <c r="N178" t="inlineStr"/>
+      <c r="O178" t="inlineStr"/>
+      <c r="P178" t="inlineStr"/>
+      <c r="Q178" t="inlineStr"/>
+      <c r="R178" t="inlineStr"/>
+      <c r="S178" t="inlineStr"/>
+      <c r="T178" t="inlineStr"/>
+      <c r="U178" t="inlineStr"/>
+      <c r="V178" t="inlineStr"/>
+      <c r="W178" t="inlineStr"/>
+      <c r="X178" t="inlineStr"/>
+      <c r="Y178" t="inlineStr"/>
+      <c r="Z178" t="inlineStr"/>
+      <c r="AA178" t="inlineStr"/>
+      <c r="AB178" t="inlineStr"/>
+      <c r="AC178" t="inlineStr"/>
+      <c r="AD178" t="inlineStr"/>
+      <c r="AE178" t="inlineStr"/>
+      <c r="AF178" t="inlineStr"/>
+      <c r="AG178" t="inlineStr"/>
+      <c r="AH178" t="inlineStr"/>
+      <c r="AI178" t="inlineStr"/>
+      <c r="AJ178" t="inlineStr"/>
+      <c r="AK178" t="inlineStr"/>
+      <c r="AL178" t="inlineStr"/>
+      <c r="AM178" t="inlineStr"/>
+      <c r="AN178" t="inlineStr"/>
+      <c r="AO178" t="inlineStr"/>
+      <c r="AP178" t="inlineStr"/>
+      <c r="AQ178" t="inlineStr"/>
+      <c r="AR178" t="inlineStr"/>
+      <c r="AS178" t="inlineStr"/>
+      <c r="AT178" t="inlineStr"/>
+      <c r="AU178" t="inlineStr"/>
+      <c r="AV178" t="inlineStr"/>
+      <c r="AW178" t="inlineStr"/>
+      <c r="AX178" t="inlineStr"/>
+      <c r="AY178" t="inlineStr"/>
+      <c r="AZ178" t="inlineStr"/>
+      <c r="BA178" t="inlineStr"/>
+      <c r="BB178" t="inlineStr"/>
+      <c r="BC178" t="inlineStr"/>
+      <c r="BD178" t="inlineStr"/>
+      <c r="BE178" t="inlineStr"/>
+      <c r="BF178" t="inlineStr"/>
+      <c r="BG178" t="inlineStr"/>
+      <c r="BH178" t="inlineStr"/>
+      <c r="BI178" t="inlineStr"/>
+      <c r="BJ178" t="inlineStr"/>
+      <c r="BK178" t="inlineStr"/>
+      <c r="BL178" t="inlineStr"/>
+      <c r="BM178" t="inlineStr"/>
+      <c r="BN178" t="inlineStr"/>
+      <c r="BO178" t="inlineStr"/>
+      <c r="BP178" t="inlineStr"/>
+      <c r="BQ178" t="inlineStr"/>
+      <c r="BR178" t="inlineStr"/>
+      <c r="BS178" t="inlineStr"/>
+      <c r="BT178" t="inlineStr"/>
+      <c r="BU178" t="inlineStr"/>
+      <c r="BV178" t="inlineStr"/>
+      <c r="BW178" t="inlineStr"/>
+      <c r="BX178" t="inlineStr"/>
+      <c r="BY178" t="inlineStr"/>
+      <c r="BZ178" t="inlineStr"/>
+      <c r="CA178" t="inlineStr"/>
+      <c r="CB178" t="inlineStr"/>
+      <c r="CC178" t="inlineStr"/>
+      <c r="CD178" t="inlineStr"/>
+      <c r="CE178" t="inlineStr"/>
+      <c r="CF178" t="inlineStr"/>
+      <c r="CG178" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gafor_log.xlsx
+++ b/data/gafor_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CG178"/>
+  <dimension ref="A1:CG179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24030,6 +24030,137 @@
       <c r="CF178" t="inlineStr"/>
       <c r="CG178" t="inlineStr"/>
     </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2026-09-12 08:00</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Ostfriesland</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Nordfriesland-Dithmarschen</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Schleswig-Holsteinische Geest</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Schleswig-Holsteinisches Hügelland</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>Nordwestliches Niedersachsen</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>Lüneburger Heide</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Westliches Niedersachsen</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>Hannover und Braunschweig</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>Teutoburger Wald</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Weser-Leine-Bergland</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr"/>
+      <c r="M179" t="inlineStr"/>
+      <c r="N179" t="inlineStr"/>
+      <c r="O179" t="inlineStr"/>
+      <c r="P179" t="inlineStr"/>
+      <c r="Q179" t="inlineStr"/>
+      <c r="R179" t="inlineStr"/>
+      <c r="S179" t="inlineStr"/>
+      <c r="T179" t="inlineStr"/>
+      <c r="U179" t="inlineStr"/>
+      <c r="V179" t="inlineStr"/>
+      <c r="W179" t="inlineStr"/>
+      <c r="X179" t="inlineStr"/>
+      <c r="Y179" t="inlineStr"/>
+      <c r="Z179" t="inlineStr"/>
+      <c r="AA179" t="inlineStr"/>
+      <c r="AB179" t="inlineStr"/>
+      <c r="AC179" t="inlineStr"/>
+      <c r="AD179" t="inlineStr"/>
+      <c r="AE179" t="inlineStr"/>
+      <c r="AF179" t="inlineStr"/>
+      <c r="AG179" t="inlineStr"/>
+      <c r="AH179" t="inlineStr"/>
+      <c r="AI179" t="inlineStr"/>
+      <c r="AJ179" t="inlineStr"/>
+      <c r="AK179" t="inlineStr"/>
+      <c r="AL179" t="inlineStr"/>
+      <c r="AM179" t="inlineStr"/>
+      <c r="AN179" t="inlineStr"/>
+      <c r="AO179" t="inlineStr"/>
+      <c r="AP179" t="inlineStr"/>
+      <c r="AQ179" t="inlineStr"/>
+      <c r="AR179" t="inlineStr"/>
+      <c r="AS179" t="inlineStr"/>
+      <c r="AT179" t="inlineStr"/>
+      <c r="AU179" t="inlineStr"/>
+      <c r="AV179" t="inlineStr"/>
+      <c r="AW179" t="inlineStr"/>
+      <c r="AX179" t="inlineStr"/>
+      <c r="AY179" t="inlineStr"/>
+      <c r="AZ179" t="inlineStr"/>
+      <c r="BA179" t="inlineStr"/>
+      <c r="BB179" t="inlineStr"/>
+      <c r="BC179" t="inlineStr"/>
+      <c r="BD179" t="inlineStr"/>
+      <c r="BE179" t="inlineStr"/>
+      <c r="BF179" t="inlineStr"/>
+      <c r="BG179" t="inlineStr"/>
+      <c r="BH179" t="inlineStr"/>
+      <c r="BI179" t="inlineStr"/>
+      <c r="BJ179" t="inlineStr"/>
+      <c r="BK179" t="inlineStr"/>
+      <c r="BL179" t="inlineStr"/>
+      <c r="BM179" t="inlineStr"/>
+      <c r="BN179" t="inlineStr"/>
+      <c r="BO179" t="inlineStr"/>
+      <c r="BP179" t="inlineStr"/>
+      <c r="BQ179" t="inlineStr"/>
+      <c r="BR179" t="inlineStr"/>
+      <c r="BS179" t="inlineStr"/>
+      <c r="BT179" t="inlineStr"/>
+      <c r="BU179" t="inlineStr"/>
+      <c r="BV179" t="inlineStr"/>
+      <c r="BW179" t="inlineStr"/>
+      <c r="BX179" t="inlineStr"/>
+      <c r="BY179" t="inlineStr"/>
+      <c r="BZ179" t="inlineStr"/>
+      <c r="CA179" t="inlineStr"/>
+      <c r="CB179" t="inlineStr"/>
+      <c r="CC179" t="inlineStr"/>
+      <c r="CD179" t="inlineStr"/>
+      <c r="CE179" t="inlineStr"/>
+      <c r="CF179" t="inlineStr"/>
+      <c r="CG179" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gafor_log.xlsx
+++ b/data/gafor_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CG179"/>
+  <dimension ref="A1:CG180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24161,6 +24161,137 @@
       <c r="CF179" t="inlineStr"/>
       <c r="CG179" t="inlineStr"/>
     </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2026-09-14 08:00</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Ostfriesland</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Nordfriesland-Dithmarschen</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Schleswig-Holsteinische Geest</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Schleswig-Holsteinisches Hügelland</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Nordwestliches Niedersachsen</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>Lüneburger Heide</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Westliches Niedersachsen</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>Hannover und Braunschweig</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>Teutoburger Wald</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Weser-Leine-Bergland</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr"/>
+      <c r="M180" t="inlineStr"/>
+      <c r="N180" t="inlineStr"/>
+      <c r="O180" t="inlineStr"/>
+      <c r="P180" t="inlineStr"/>
+      <c r="Q180" t="inlineStr"/>
+      <c r="R180" t="inlineStr"/>
+      <c r="S180" t="inlineStr"/>
+      <c r="T180" t="inlineStr"/>
+      <c r="U180" t="inlineStr"/>
+      <c r="V180" t="inlineStr"/>
+      <c r="W180" t="inlineStr"/>
+      <c r="X180" t="inlineStr"/>
+      <c r="Y180" t="inlineStr"/>
+      <c r="Z180" t="inlineStr"/>
+      <c r="AA180" t="inlineStr"/>
+      <c r="AB180" t="inlineStr"/>
+      <c r="AC180" t="inlineStr"/>
+      <c r="AD180" t="inlineStr"/>
+      <c r="AE180" t="inlineStr"/>
+      <c r="AF180" t="inlineStr"/>
+      <c r="AG180" t="inlineStr"/>
+      <c r="AH180" t="inlineStr"/>
+      <c r="AI180" t="inlineStr"/>
+      <c r="AJ180" t="inlineStr"/>
+      <c r="AK180" t="inlineStr"/>
+      <c r="AL180" t="inlineStr"/>
+      <c r="AM180" t="inlineStr"/>
+      <c r="AN180" t="inlineStr"/>
+      <c r="AO180" t="inlineStr"/>
+      <c r="AP180" t="inlineStr"/>
+      <c r="AQ180" t="inlineStr"/>
+      <c r="AR180" t="inlineStr"/>
+      <c r="AS180" t="inlineStr"/>
+      <c r="AT180" t="inlineStr"/>
+      <c r="AU180" t="inlineStr"/>
+      <c r="AV180" t="inlineStr"/>
+      <c r="AW180" t="inlineStr"/>
+      <c r="AX180" t="inlineStr"/>
+      <c r="AY180" t="inlineStr"/>
+      <c r="AZ180" t="inlineStr"/>
+      <c r="BA180" t="inlineStr"/>
+      <c r="BB180" t="inlineStr"/>
+      <c r="BC180" t="inlineStr"/>
+      <c r="BD180" t="inlineStr"/>
+      <c r="BE180" t="inlineStr"/>
+      <c r="BF180" t="inlineStr"/>
+      <c r="BG180" t="inlineStr"/>
+      <c r="BH180" t="inlineStr"/>
+      <c r="BI180" t="inlineStr"/>
+      <c r="BJ180" t="inlineStr"/>
+      <c r="BK180" t="inlineStr"/>
+      <c r="BL180" t="inlineStr"/>
+      <c r="BM180" t="inlineStr"/>
+      <c r="BN180" t="inlineStr"/>
+      <c r="BO180" t="inlineStr"/>
+      <c r="BP180" t="inlineStr"/>
+      <c r="BQ180" t="inlineStr"/>
+      <c r="BR180" t="inlineStr"/>
+      <c r="BS180" t="inlineStr"/>
+      <c r="BT180" t="inlineStr"/>
+      <c r="BU180" t="inlineStr"/>
+      <c r="BV180" t="inlineStr"/>
+      <c r="BW180" t="inlineStr"/>
+      <c r="BX180" t="inlineStr"/>
+      <c r="BY180" t="inlineStr"/>
+      <c r="BZ180" t="inlineStr"/>
+      <c r="CA180" t="inlineStr"/>
+      <c r="CB180" t="inlineStr"/>
+      <c r="CC180" t="inlineStr"/>
+      <c r="CD180" t="inlineStr"/>
+      <c r="CE180" t="inlineStr"/>
+      <c r="CF180" t="inlineStr"/>
+      <c r="CG180" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gafor_log.xlsx
+++ b/data/gafor_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CG180"/>
+  <dimension ref="A1:CG181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24292,6 +24292,137 @@
       <c r="CF180" t="inlineStr"/>
       <c r="CG180" t="inlineStr"/>
     </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2026-09-15 08:00</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Ostfriesland</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Nordfriesland-Dithmarschen</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Schleswig-Holsteinische Geest</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Schleswig-Holsteinisches Hügelland</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Nordwestliches Niedersachsen</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>Lüneburger Heide</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Westliches Niedersachsen</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>Hannover und Braunschweig</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>Teutoburger Wald</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Weser-Leine-Bergland</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr"/>
+      <c r="M181" t="inlineStr"/>
+      <c r="N181" t="inlineStr"/>
+      <c r="O181" t="inlineStr"/>
+      <c r="P181" t="inlineStr"/>
+      <c r="Q181" t="inlineStr"/>
+      <c r="R181" t="inlineStr"/>
+      <c r="S181" t="inlineStr"/>
+      <c r="T181" t="inlineStr"/>
+      <c r="U181" t="inlineStr"/>
+      <c r="V181" t="inlineStr"/>
+      <c r="W181" t="inlineStr"/>
+      <c r="X181" t="inlineStr"/>
+      <c r="Y181" t="inlineStr"/>
+      <c r="Z181" t="inlineStr"/>
+      <c r="AA181" t="inlineStr"/>
+      <c r="AB181" t="inlineStr"/>
+      <c r="AC181" t="inlineStr"/>
+      <c r="AD181" t="inlineStr"/>
+      <c r="AE181" t="inlineStr"/>
+      <c r="AF181" t="inlineStr"/>
+      <c r="AG181" t="inlineStr"/>
+      <c r="AH181" t="inlineStr"/>
+      <c r="AI181" t="inlineStr"/>
+      <c r="AJ181" t="inlineStr"/>
+      <c r="AK181" t="inlineStr"/>
+      <c r="AL181" t="inlineStr"/>
+      <c r="AM181" t="inlineStr"/>
+      <c r="AN181" t="inlineStr"/>
+      <c r="AO181" t="inlineStr"/>
+      <c r="AP181" t="inlineStr"/>
+      <c r="AQ181" t="inlineStr"/>
+      <c r="AR181" t="inlineStr"/>
+      <c r="AS181" t="inlineStr"/>
+      <c r="AT181" t="inlineStr"/>
+      <c r="AU181" t="inlineStr"/>
+      <c r="AV181" t="inlineStr"/>
+      <c r="AW181" t="inlineStr"/>
+      <c r="AX181" t="inlineStr"/>
+      <c r="AY181" t="inlineStr"/>
+      <c r="AZ181" t="inlineStr"/>
+      <c r="BA181" t="inlineStr"/>
+      <c r="BB181" t="inlineStr"/>
+      <c r="BC181" t="inlineStr"/>
+      <c r="BD181" t="inlineStr"/>
+      <c r="BE181" t="inlineStr"/>
+      <c r="BF181" t="inlineStr"/>
+      <c r="BG181" t="inlineStr"/>
+      <c r="BH181" t="inlineStr"/>
+      <c r="BI181" t="inlineStr"/>
+      <c r="BJ181" t="inlineStr"/>
+      <c r="BK181" t="inlineStr"/>
+      <c r="BL181" t="inlineStr"/>
+      <c r="BM181" t="inlineStr"/>
+      <c r="BN181" t="inlineStr"/>
+      <c r="BO181" t="inlineStr"/>
+      <c r="BP181" t="inlineStr"/>
+      <c r="BQ181" t="inlineStr"/>
+      <c r="BR181" t="inlineStr"/>
+      <c r="BS181" t="inlineStr"/>
+      <c r="BT181" t="inlineStr"/>
+      <c r="BU181" t="inlineStr"/>
+      <c r="BV181" t="inlineStr"/>
+      <c r="BW181" t="inlineStr"/>
+      <c r="BX181" t="inlineStr"/>
+      <c r="BY181" t="inlineStr"/>
+      <c r="BZ181" t="inlineStr"/>
+      <c r="CA181" t="inlineStr"/>
+      <c r="CB181" t="inlineStr"/>
+      <c r="CC181" t="inlineStr"/>
+      <c r="CD181" t="inlineStr"/>
+      <c r="CE181" t="inlineStr"/>
+      <c r="CF181" t="inlineStr"/>
+      <c r="CG181" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gafor_log.xlsx
+++ b/data/gafor_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CG181"/>
+  <dimension ref="A1:CG182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24423,6 +24423,137 @@
       <c r="CF181" t="inlineStr"/>
       <c r="CG181" t="inlineStr"/>
     </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2026-09-16 08:00</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Ostfriesland</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Nordfriesland-Dithmarschen</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Schleswig-Holsteinische Geest</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Schleswig-Holsteinisches Hügelland</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>Nordwestliches Niedersachsen</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>Lüneburger Heide</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Westliches Niedersachsen</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>Hannover und Braunschweig</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>Teutoburger Wald</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Weser-Leine-Bergland</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr"/>
+      <c r="M182" t="inlineStr"/>
+      <c r="N182" t="inlineStr"/>
+      <c r="O182" t="inlineStr"/>
+      <c r="P182" t="inlineStr"/>
+      <c r="Q182" t="inlineStr"/>
+      <c r="R182" t="inlineStr"/>
+      <c r="S182" t="inlineStr"/>
+      <c r="T182" t="inlineStr"/>
+      <c r="U182" t="inlineStr"/>
+      <c r="V182" t="inlineStr"/>
+      <c r="W182" t="inlineStr"/>
+      <c r="X182" t="inlineStr"/>
+      <c r="Y182" t="inlineStr"/>
+      <c r="Z182" t="inlineStr"/>
+      <c r="AA182" t="inlineStr"/>
+      <c r="AB182" t="inlineStr"/>
+      <c r="AC182" t="inlineStr"/>
+      <c r="AD182" t="inlineStr"/>
+      <c r="AE182" t="inlineStr"/>
+      <c r="AF182" t="inlineStr"/>
+      <c r="AG182" t="inlineStr"/>
+      <c r="AH182" t="inlineStr"/>
+      <c r="AI182" t="inlineStr"/>
+      <c r="AJ182" t="inlineStr"/>
+      <c r="AK182" t="inlineStr"/>
+      <c r="AL182" t="inlineStr"/>
+      <c r="AM182" t="inlineStr"/>
+      <c r="AN182" t="inlineStr"/>
+      <c r="AO182" t="inlineStr"/>
+      <c r="AP182" t="inlineStr"/>
+      <c r="AQ182" t="inlineStr"/>
+      <c r="AR182" t="inlineStr"/>
+      <c r="AS182" t="inlineStr"/>
+      <c r="AT182" t="inlineStr"/>
+      <c r="AU182" t="inlineStr"/>
+      <c r="AV182" t="inlineStr"/>
+      <c r="AW182" t="inlineStr"/>
+      <c r="AX182" t="inlineStr"/>
+      <c r="AY182" t="inlineStr"/>
+      <c r="AZ182" t="inlineStr"/>
+      <c r="BA182" t="inlineStr"/>
+      <c r="BB182" t="inlineStr"/>
+      <c r="BC182" t="inlineStr"/>
+      <c r="BD182" t="inlineStr"/>
+      <c r="BE182" t="inlineStr"/>
+      <c r="BF182" t="inlineStr"/>
+      <c r="BG182" t="inlineStr"/>
+      <c r="BH182" t="inlineStr"/>
+      <c r="BI182" t="inlineStr"/>
+      <c r="BJ182" t="inlineStr"/>
+      <c r="BK182" t="inlineStr"/>
+      <c r="BL182" t="inlineStr"/>
+      <c r="BM182" t="inlineStr"/>
+      <c r="BN182" t="inlineStr"/>
+      <c r="BO182" t="inlineStr"/>
+      <c r="BP182" t="inlineStr"/>
+      <c r="BQ182" t="inlineStr"/>
+      <c r="BR182" t="inlineStr"/>
+      <c r="BS182" t="inlineStr"/>
+      <c r="BT182" t="inlineStr"/>
+      <c r="BU182" t="inlineStr"/>
+      <c r="BV182" t="inlineStr"/>
+      <c r="BW182" t="inlineStr"/>
+      <c r="BX182" t="inlineStr"/>
+      <c r="BY182" t="inlineStr"/>
+      <c r="BZ182" t="inlineStr"/>
+      <c r="CA182" t="inlineStr"/>
+      <c r="CB182" t="inlineStr"/>
+      <c r="CC182" t="inlineStr"/>
+      <c r="CD182" t="inlineStr"/>
+      <c r="CE182" t="inlineStr"/>
+      <c r="CF182" t="inlineStr"/>
+      <c r="CG182" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gafor_log.xlsx
+++ b/data/gafor_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CG182"/>
+  <dimension ref="A1:CG183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24554,6 +24554,137 @@
       <c r="CF182" t="inlineStr"/>
       <c r="CG182" t="inlineStr"/>
     </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2026-09-18 08:00</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Ostfriesland</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Nordfriesland-Dithmarschen</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Schleswig-Holsteinische Geest</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Schleswig-Holsteinisches Hügelland</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Nordwestliches Niedersachsen</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>Lüneburger Heide</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Westliches Niedersachsen</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>Hannover und Braunschweig</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>Teutoburger Wald</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Weser-Leine-Bergland</t>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr"/>
+      <c r="M183" t="inlineStr"/>
+      <c r="N183" t="inlineStr"/>
+      <c r="O183" t="inlineStr"/>
+      <c r="P183" t="inlineStr"/>
+      <c r="Q183" t="inlineStr"/>
+      <c r="R183" t="inlineStr"/>
+      <c r="S183" t="inlineStr"/>
+      <c r="T183" t="inlineStr"/>
+      <c r="U183" t="inlineStr"/>
+      <c r="V183" t="inlineStr"/>
+      <c r="W183" t="inlineStr"/>
+      <c r="X183" t="inlineStr"/>
+      <c r="Y183" t="inlineStr"/>
+      <c r="Z183" t="inlineStr"/>
+      <c r="AA183" t="inlineStr"/>
+      <c r="AB183" t="inlineStr"/>
+      <c r="AC183" t="inlineStr"/>
+      <c r="AD183" t="inlineStr"/>
+      <c r="AE183" t="inlineStr"/>
+      <c r="AF183" t="inlineStr"/>
+      <c r="AG183" t="inlineStr"/>
+      <c r="AH183" t="inlineStr"/>
+      <c r="AI183" t="inlineStr"/>
+      <c r="AJ183" t="inlineStr"/>
+      <c r="AK183" t="inlineStr"/>
+      <c r="AL183" t="inlineStr"/>
+      <c r="AM183" t="inlineStr"/>
+      <c r="AN183" t="inlineStr"/>
+      <c r="AO183" t="inlineStr"/>
+      <c r="AP183" t="inlineStr"/>
+      <c r="AQ183" t="inlineStr"/>
+      <c r="AR183" t="inlineStr"/>
+      <c r="AS183" t="inlineStr"/>
+      <c r="AT183" t="inlineStr"/>
+      <c r="AU183" t="inlineStr"/>
+      <c r="AV183" t="inlineStr"/>
+      <c r="AW183" t="inlineStr"/>
+      <c r="AX183" t="inlineStr"/>
+      <c r="AY183" t="inlineStr"/>
+      <c r="AZ183" t="inlineStr"/>
+      <c r="BA183" t="inlineStr"/>
+      <c r="BB183" t="inlineStr"/>
+      <c r="BC183" t="inlineStr"/>
+      <c r="BD183" t="inlineStr"/>
+      <c r="BE183" t="inlineStr"/>
+      <c r="BF183" t="inlineStr"/>
+      <c r="BG183" t="inlineStr"/>
+      <c r="BH183" t="inlineStr"/>
+      <c r="BI183" t="inlineStr"/>
+      <c r="BJ183" t="inlineStr"/>
+      <c r="BK183" t="inlineStr"/>
+      <c r="BL183" t="inlineStr"/>
+      <c r="BM183" t="inlineStr"/>
+      <c r="BN183" t="inlineStr"/>
+      <c r="BO183" t="inlineStr"/>
+      <c r="BP183" t="inlineStr"/>
+      <c r="BQ183" t="inlineStr"/>
+      <c r="BR183" t="inlineStr"/>
+      <c r="BS183" t="inlineStr"/>
+      <c r="BT183" t="inlineStr"/>
+      <c r="BU183" t="inlineStr"/>
+      <c r="BV183" t="inlineStr"/>
+      <c r="BW183" t="inlineStr"/>
+      <c r="BX183" t="inlineStr"/>
+      <c r="BY183" t="inlineStr"/>
+      <c r="BZ183" t="inlineStr"/>
+      <c r="CA183" t="inlineStr"/>
+      <c r="CB183" t="inlineStr"/>
+      <c r="CC183" t="inlineStr"/>
+      <c r="CD183" t="inlineStr"/>
+      <c r="CE183" t="inlineStr"/>
+      <c r="CF183" t="inlineStr"/>
+      <c r="CG183" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gafor_log.xlsx
+++ b/data/gafor_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CG183"/>
+  <dimension ref="A1:CG184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24685,6 +24685,137 @@
       <c r="CF183" t="inlineStr"/>
       <c r="CG183" t="inlineStr"/>
     </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2026-09-21 08:00</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Ostfriesland</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Nordfriesland-Dithmarschen</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Schleswig-Holsteinische Geest</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Schleswig-Holsteinisches Hügelland</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Nordwestliches Niedersachsen</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>Lüneburger Heide</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Westliches Niedersachsen</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>Hannover und Braunschweig</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>Teutoburger Wald</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Weser-Leine-Bergland</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr"/>
+      <c r="M184" t="inlineStr"/>
+      <c r="N184" t="inlineStr"/>
+      <c r="O184" t="inlineStr"/>
+      <c r="P184" t="inlineStr"/>
+      <c r="Q184" t="inlineStr"/>
+      <c r="R184" t="inlineStr"/>
+      <c r="S184" t="inlineStr"/>
+      <c r="T184" t="inlineStr"/>
+      <c r="U184" t="inlineStr"/>
+      <c r="V184" t="inlineStr"/>
+      <c r="W184" t="inlineStr"/>
+      <c r="X184" t="inlineStr"/>
+      <c r="Y184" t="inlineStr"/>
+      <c r="Z184" t="inlineStr"/>
+      <c r="AA184" t="inlineStr"/>
+      <c r="AB184" t="inlineStr"/>
+      <c r="AC184" t="inlineStr"/>
+      <c r="AD184" t="inlineStr"/>
+      <c r="AE184" t="inlineStr"/>
+      <c r="AF184" t="inlineStr"/>
+      <c r="AG184" t="inlineStr"/>
+      <c r="AH184" t="inlineStr"/>
+      <c r="AI184" t="inlineStr"/>
+      <c r="AJ184" t="inlineStr"/>
+      <c r="AK184" t="inlineStr"/>
+      <c r="AL184" t="inlineStr"/>
+      <c r="AM184" t="inlineStr"/>
+      <c r="AN184" t="inlineStr"/>
+      <c r="AO184" t="inlineStr"/>
+      <c r="AP184" t="inlineStr"/>
+      <c r="AQ184" t="inlineStr"/>
+      <c r="AR184" t="inlineStr"/>
+      <c r="AS184" t="inlineStr"/>
+      <c r="AT184" t="inlineStr"/>
+      <c r="AU184" t="inlineStr"/>
+      <c r="AV184" t="inlineStr"/>
+      <c r="AW184" t="inlineStr"/>
+      <c r="AX184" t="inlineStr"/>
+      <c r="AY184" t="inlineStr"/>
+      <c r="AZ184" t="inlineStr"/>
+      <c r="BA184" t="inlineStr"/>
+      <c r="BB184" t="inlineStr"/>
+      <c r="BC184" t="inlineStr"/>
+      <c r="BD184" t="inlineStr"/>
+      <c r="BE184" t="inlineStr"/>
+      <c r="BF184" t="inlineStr"/>
+      <c r="BG184" t="inlineStr"/>
+      <c r="BH184" t="inlineStr"/>
+      <c r="BI184" t="inlineStr"/>
+      <c r="BJ184" t="inlineStr"/>
+      <c r="BK184" t="inlineStr"/>
+      <c r="BL184" t="inlineStr"/>
+      <c r="BM184" t="inlineStr"/>
+      <c r="BN184" t="inlineStr"/>
+      <c r="BO184" t="inlineStr"/>
+      <c r="BP184" t="inlineStr"/>
+      <c r="BQ184" t="inlineStr"/>
+      <c r="BR184" t="inlineStr"/>
+      <c r="BS184" t="inlineStr"/>
+      <c r="BT184" t="inlineStr"/>
+      <c r="BU184" t="inlineStr"/>
+      <c r="BV184" t="inlineStr"/>
+      <c r="BW184" t="inlineStr"/>
+      <c r="BX184" t="inlineStr"/>
+      <c r="BY184" t="inlineStr"/>
+      <c r="BZ184" t="inlineStr"/>
+      <c r="CA184" t="inlineStr"/>
+      <c r="CB184" t="inlineStr"/>
+      <c r="CC184" t="inlineStr"/>
+      <c r="CD184" t="inlineStr"/>
+      <c r="CE184" t="inlineStr"/>
+      <c r="CF184" t="inlineStr"/>
+      <c r="CG184" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gafor_log.xlsx
+++ b/data/gafor_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CG184"/>
+  <dimension ref="A1:CG185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24816,6 +24816,137 @@
       <c r="CF184" t="inlineStr"/>
       <c r="CG184" t="inlineStr"/>
     </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026-09-22 08:00</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Ostfriesland</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Nordfriesland-Dithmarschen</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Schleswig-Holsteinische Geest</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Schleswig-Holsteinisches Hügelland</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Nordwestliches Niedersachsen</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>Lüneburger Heide</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Westliches Niedersachsen</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>Hannover und Braunschweig</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>Teutoburger Wald</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Weser-Leine-Bergland</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr"/>
+      <c r="M185" t="inlineStr"/>
+      <c r="N185" t="inlineStr"/>
+      <c r="O185" t="inlineStr"/>
+      <c r="P185" t="inlineStr"/>
+      <c r="Q185" t="inlineStr"/>
+      <c r="R185" t="inlineStr"/>
+      <c r="S185" t="inlineStr"/>
+      <c r="T185" t="inlineStr"/>
+      <c r="U185" t="inlineStr"/>
+      <c r="V185" t="inlineStr"/>
+      <c r="W185" t="inlineStr"/>
+      <c r="X185" t="inlineStr"/>
+      <c r="Y185" t="inlineStr"/>
+      <c r="Z185" t="inlineStr"/>
+      <c r="AA185" t="inlineStr"/>
+      <c r="AB185" t="inlineStr"/>
+      <c r="AC185" t="inlineStr"/>
+      <c r="AD185" t="inlineStr"/>
+      <c r="AE185" t="inlineStr"/>
+      <c r="AF185" t="inlineStr"/>
+      <c r="AG185" t="inlineStr"/>
+      <c r="AH185" t="inlineStr"/>
+      <c r="AI185" t="inlineStr"/>
+      <c r="AJ185" t="inlineStr"/>
+      <c r="AK185" t="inlineStr"/>
+      <c r="AL185" t="inlineStr"/>
+      <c r="AM185" t="inlineStr"/>
+      <c r="AN185" t="inlineStr"/>
+      <c r="AO185" t="inlineStr"/>
+      <c r="AP185" t="inlineStr"/>
+      <c r="AQ185" t="inlineStr"/>
+      <c r="AR185" t="inlineStr"/>
+      <c r="AS185" t="inlineStr"/>
+      <c r="AT185" t="inlineStr"/>
+      <c r="AU185" t="inlineStr"/>
+      <c r="AV185" t="inlineStr"/>
+      <c r="AW185" t="inlineStr"/>
+      <c r="AX185" t="inlineStr"/>
+      <c r="AY185" t="inlineStr"/>
+      <c r="AZ185" t="inlineStr"/>
+      <c r="BA185" t="inlineStr"/>
+      <c r="BB185" t="inlineStr"/>
+      <c r="BC185" t="inlineStr"/>
+      <c r="BD185" t="inlineStr"/>
+      <c r="BE185" t="inlineStr"/>
+      <c r="BF185" t="inlineStr"/>
+      <c r="BG185" t="inlineStr"/>
+      <c r="BH185" t="inlineStr"/>
+      <c r="BI185" t="inlineStr"/>
+      <c r="BJ185" t="inlineStr"/>
+      <c r="BK185" t="inlineStr"/>
+      <c r="BL185" t="inlineStr"/>
+      <c r="BM185" t="inlineStr"/>
+      <c r="BN185" t="inlineStr"/>
+      <c r="BO185" t="inlineStr"/>
+      <c r="BP185" t="inlineStr"/>
+      <c r="BQ185" t="inlineStr"/>
+      <c r="BR185" t="inlineStr"/>
+      <c r="BS185" t="inlineStr"/>
+      <c r="BT185" t="inlineStr"/>
+      <c r="BU185" t="inlineStr"/>
+      <c r="BV185" t="inlineStr"/>
+      <c r="BW185" t="inlineStr"/>
+      <c r="BX185" t="inlineStr"/>
+      <c r="BY185" t="inlineStr"/>
+      <c r="BZ185" t="inlineStr"/>
+      <c r="CA185" t="inlineStr"/>
+      <c r="CB185" t="inlineStr"/>
+      <c r="CC185" t="inlineStr"/>
+      <c r="CD185" t="inlineStr"/>
+      <c r="CE185" t="inlineStr"/>
+      <c r="CF185" t="inlineStr"/>
+      <c r="CG185" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gafor_log.xlsx
+++ b/data/gafor_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CG185"/>
+  <dimension ref="A1:CG186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24947,6 +24947,137 @@
       <c r="CF185" t="inlineStr"/>
       <c r="CG185" t="inlineStr"/>
     </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2026-09-23 08:00</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Ostfriesland</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Nordfriesland-Dithmarschen</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Schleswig-Holsteinische Geest</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Schleswig-Holsteinisches Hügelland</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Nordwestliches Niedersachsen</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>Lüneburger Heide</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Westliches Niedersachsen</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>Hannover und Braunschweig</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>Teutoburger Wald</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Weser-Leine-Bergland</t>
+        </is>
+      </c>
+      <c r="L186" t="inlineStr"/>
+      <c r="M186" t="inlineStr"/>
+      <c r="N186" t="inlineStr"/>
+      <c r="O186" t="inlineStr"/>
+      <c r="P186" t="inlineStr"/>
+      <c r="Q186" t="inlineStr"/>
+      <c r="R186" t="inlineStr"/>
+      <c r="S186" t="inlineStr"/>
+      <c r="T186" t="inlineStr"/>
+      <c r="U186" t="inlineStr"/>
+      <c r="V186" t="inlineStr"/>
+      <c r="W186" t="inlineStr"/>
+      <c r="X186" t="inlineStr"/>
+      <c r="Y186" t="inlineStr"/>
+      <c r="Z186" t="inlineStr"/>
+      <c r="AA186" t="inlineStr"/>
+      <c r="AB186" t="inlineStr"/>
+      <c r="AC186" t="inlineStr"/>
+      <c r="AD186" t="inlineStr"/>
+      <c r="AE186" t="inlineStr"/>
+      <c r="AF186" t="inlineStr"/>
+      <c r="AG186" t="inlineStr"/>
+      <c r="AH186" t="inlineStr"/>
+      <c r="AI186" t="inlineStr"/>
+      <c r="AJ186" t="inlineStr"/>
+      <c r="AK186" t="inlineStr"/>
+      <c r="AL186" t="inlineStr"/>
+      <c r="AM186" t="inlineStr"/>
+      <c r="AN186" t="inlineStr"/>
+      <c r="AO186" t="inlineStr"/>
+      <c r="AP186" t="inlineStr"/>
+      <c r="AQ186" t="inlineStr"/>
+      <c r="AR186" t="inlineStr"/>
+      <c r="AS186" t="inlineStr"/>
+      <c r="AT186" t="inlineStr"/>
+      <c r="AU186" t="inlineStr"/>
+      <c r="AV186" t="inlineStr"/>
+      <c r="AW186" t="inlineStr"/>
+      <c r="AX186" t="inlineStr"/>
+      <c r="AY186" t="inlineStr"/>
+      <c r="AZ186" t="inlineStr"/>
+      <c r="BA186" t="inlineStr"/>
+      <c r="BB186" t="inlineStr"/>
+      <c r="BC186" t="inlineStr"/>
+      <c r="BD186" t="inlineStr"/>
+      <c r="BE186" t="inlineStr"/>
+      <c r="BF186" t="inlineStr"/>
+      <c r="BG186" t="inlineStr"/>
+      <c r="BH186" t="inlineStr"/>
+      <c r="BI186" t="inlineStr"/>
+      <c r="BJ186" t="inlineStr"/>
+      <c r="BK186" t="inlineStr"/>
+      <c r="BL186" t="inlineStr"/>
+      <c r="BM186" t="inlineStr"/>
+      <c r="BN186" t="inlineStr"/>
+      <c r="BO186" t="inlineStr"/>
+      <c r="BP186" t="inlineStr"/>
+      <c r="BQ186" t="inlineStr"/>
+      <c r="BR186" t="inlineStr"/>
+      <c r="BS186" t="inlineStr"/>
+      <c r="BT186" t="inlineStr"/>
+      <c r="BU186" t="inlineStr"/>
+      <c r="BV186" t="inlineStr"/>
+      <c r="BW186" t="inlineStr"/>
+      <c r="BX186" t="inlineStr"/>
+      <c r="BY186" t="inlineStr"/>
+      <c r="BZ186" t="inlineStr"/>
+      <c r="CA186" t="inlineStr"/>
+      <c r="CB186" t="inlineStr"/>
+      <c r="CC186" t="inlineStr"/>
+      <c r="CD186" t="inlineStr"/>
+      <c r="CE186" t="inlineStr"/>
+      <c r="CF186" t="inlineStr"/>
+      <c r="CG186" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gafor_log.xlsx
+++ b/data/gafor_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CG186"/>
+  <dimension ref="A1:CG187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25078,6 +25078,137 @@
       <c r="CF186" t="inlineStr"/>
       <c r="CG186" t="inlineStr"/>
     </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2026-09-24 08:00</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Ostfriesland</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Nordfriesland-Dithmarschen</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Schleswig-Holsteinische Geest</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Schleswig-Holsteinisches Hügelland</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Nordwestliches Niedersachsen</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>Lüneburger Heide</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Westliches Niedersachsen</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>Hannover und Braunschweig</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>Teutoburger Wald</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Weser-Leine-Bergland</t>
+        </is>
+      </c>
+      <c r="L187" t="inlineStr"/>
+      <c r="M187" t="inlineStr"/>
+      <c r="N187" t="inlineStr"/>
+      <c r="O187" t="inlineStr"/>
+      <c r="P187" t="inlineStr"/>
+      <c r="Q187" t="inlineStr"/>
+      <c r="R187" t="inlineStr"/>
+      <c r="S187" t="inlineStr"/>
+      <c r="T187" t="inlineStr"/>
+      <c r="U187" t="inlineStr"/>
+      <c r="V187" t="inlineStr"/>
+      <c r="W187" t="inlineStr"/>
+      <c r="X187" t="inlineStr"/>
+      <c r="Y187" t="inlineStr"/>
+      <c r="Z187" t="inlineStr"/>
+      <c r="AA187" t="inlineStr"/>
+      <c r="AB187" t="inlineStr"/>
+      <c r="AC187" t="inlineStr"/>
+      <c r="AD187" t="inlineStr"/>
+      <c r="AE187" t="inlineStr"/>
+      <c r="AF187" t="inlineStr"/>
+      <c r="AG187" t="inlineStr"/>
+      <c r="AH187" t="inlineStr"/>
+      <c r="AI187" t="inlineStr"/>
+      <c r="AJ187" t="inlineStr"/>
+      <c r="AK187" t="inlineStr"/>
+      <c r="AL187" t="inlineStr"/>
+      <c r="AM187" t="inlineStr"/>
+      <c r="AN187" t="inlineStr"/>
+      <c r="AO187" t="inlineStr"/>
+      <c r="AP187" t="inlineStr"/>
+      <c r="AQ187" t="inlineStr"/>
+      <c r="AR187" t="inlineStr"/>
+      <c r="AS187" t="inlineStr"/>
+      <c r="AT187" t="inlineStr"/>
+      <c r="AU187" t="inlineStr"/>
+      <c r="AV187" t="inlineStr"/>
+      <c r="AW187" t="inlineStr"/>
+      <c r="AX187" t="inlineStr"/>
+      <c r="AY187" t="inlineStr"/>
+      <c r="AZ187" t="inlineStr"/>
+      <c r="BA187" t="inlineStr"/>
+      <c r="BB187" t="inlineStr"/>
+      <c r="BC187" t="inlineStr"/>
+      <c r="BD187" t="inlineStr"/>
+      <c r="BE187" t="inlineStr"/>
+      <c r="BF187" t="inlineStr"/>
+      <c r="BG187" t="inlineStr"/>
+      <c r="BH187" t="inlineStr"/>
+      <c r="BI187" t="inlineStr"/>
+      <c r="BJ187" t="inlineStr"/>
+      <c r="BK187" t="inlineStr"/>
+      <c r="BL187" t="inlineStr"/>
+      <c r="BM187" t="inlineStr"/>
+      <c r="BN187" t="inlineStr"/>
+      <c r="BO187" t="inlineStr"/>
+      <c r="BP187" t="inlineStr"/>
+      <c r="BQ187" t="inlineStr"/>
+      <c r="BR187" t="inlineStr"/>
+      <c r="BS187" t="inlineStr"/>
+      <c r="BT187" t="inlineStr"/>
+      <c r="BU187" t="inlineStr"/>
+      <c r="BV187" t="inlineStr"/>
+      <c r="BW187" t="inlineStr"/>
+      <c r="BX187" t="inlineStr"/>
+      <c r="BY187" t="inlineStr"/>
+      <c r="BZ187" t="inlineStr"/>
+      <c r="CA187" t="inlineStr"/>
+      <c r="CB187" t="inlineStr"/>
+      <c r="CC187" t="inlineStr"/>
+      <c r="CD187" t="inlineStr"/>
+      <c r="CE187" t="inlineStr"/>
+      <c r="CF187" t="inlineStr"/>
+      <c r="CG187" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gafor_log.xlsx
+++ b/data/gafor_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CG187"/>
+  <dimension ref="A1:CG188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25209,6 +25209,137 @@
       <c r="CF187" t="inlineStr"/>
       <c r="CG187" t="inlineStr"/>
     </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2026-09-25 08:00</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Ostfriesland</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Nordfriesland-Dithmarschen</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Schleswig-Holsteinische Geest</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Schleswig-Holsteinisches Hügelland</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Nordwestliches Niedersachsen</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>Lüneburger Heide</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Westliches Niedersachsen</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>Hannover und Braunschweig</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>Teutoburger Wald</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Weser-Leine-Bergland</t>
+        </is>
+      </c>
+      <c r="L188" t="inlineStr"/>
+      <c r="M188" t="inlineStr"/>
+      <c r="N188" t="inlineStr"/>
+      <c r="O188" t="inlineStr"/>
+      <c r="P188" t="inlineStr"/>
+      <c r="Q188" t="inlineStr"/>
+      <c r="R188" t="inlineStr"/>
+      <c r="S188" t="inlineStr"/>
+      <c r="T188" t="inlineStr"/>
+      <c r="U188" t="inlineStr"/>
+      <c r="V188" t="inlineStr"/>
+      <c r="W188" t="inlineStr"/>
+      <c r="X188" t="inlineStr"/>
+      <c r="Y188" t="inlineStr"/>
+      <c r="Z188" t="inlineStr"/>
+      <c r="AA188" t="inlineStr"/>
+      <c r="AB188" t="inlineStr"/>
+      <c r="AC188" t="inlineStr"/>
+      <c r="AD188" t="inlineStr"/>
+      <c r="AE188" t="inlineStr"/>
+      <c r="AF188" t="inlineStr"/>
+      <c r="AG188" t="inlineStr"/>
+      <c r="AH188" t="inlineStr"/>
+      <c r="AI188" t="inlineStr"/>
+      <c r="AJ188" t="inlineStr"/>
+      <c r="AK188" t="inlineStr"/>
+      <c r="AL188" t="inlineStr"/>
+      <c r="AM188" t="inlineStr"/>
+      <c r="AN188" t="inlineStr"/>
+      <c r="AO188" t="inlineStr"/>
+      <c r="AP188" t="inlineStr"/>
+      <c r="AQ188" t="inlineStr"/>
+      <c r="AR188" t="inlineStr"/>
+      <c r="AS188" t="inlineStr"/>
+      <c r="AT188" t="inlineStr"/>
+      <c r="AU188" t="inlineStr"/>
+      <c r="AV188" t="inlineStr"/>
+      <c r="AW188" t="inlineStr"/>
+      <c r="AX188" t="inlineStr"/>
+      <c r="AY188" t="inlineStr"/>
+      <c r="AZ188" t="inlineStr"/>
+      <c r="BA188" t="inlineStr"/>
+      <c r="BB188" t="inlineStr"/>
+      <c r="BC188" t="inlineStr"/>
+      <c r="BD188" t="inlineStr"/>
+      <c r="BE188" t="inlineStr"/>
+      <c r="BF188" t="inlineStr"/>
+      <c r="BG188" t="inlineStr"/>
+      <c r="BH188" t="inlineStr"/>
+      <c r="BI188" t="inlineStr"/>
+      <c r="BJ188" t="inlineStr"/>
+      <c r="BK188" t="inlineStr"/>
+      <c r="BL188" t="inlineStr"/>
+      <c r="BM188" t="inlineStr"/>
+      <c r="BN188" t="inlineStr"/>
+      <c r="BO188" t="inlineStr"/>
+      <c r="BP188" t="inlineStr"/>
+      <c r="BQ188" t="inlineStr"/>
+      <c r="BR188" t="inlineStr"/>
+      <c r="BS188" t="inlineStr"/>
+      <c r="BT188" t="inlineStr"/>
+      <c r="BU188" t="inlineStr"/>
+      <c r="BV188" t="inlineStr"/>
+      <c r="BW188" t="inlineStr"/>
+      <c r="BX188" t="inlineStr"/>
+      <c r="BY188" t="inlineStr"/>
+      <c r="BZ188" t="inlineStr"/>
+      <c r="CA188" t="inlineStr"/>
+      <c r="CB188" t="inlineStr"/>
+      <c r="CC188" t="inlineStr"/>
+      <c r="CD188" t="inlineStr"/>
+      <c r="CE188" t="inlineStr"/>
+      <c r="CF188" t="inlineStr"/>
+      <c r="CG188" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gafor_log.xlsx
+++ b/data/gafor_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CG188"/>
+  <dimension ref="A1:CG189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25340,6 +25340,137 @@
       <c r="CF188" t="inlineStr"/>
       <c r="CG188" t="inlineStr"/>
     </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2026-09-26 08:00</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Ostfriesland</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Nordfriesland-Dithmarschen</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Schleswig-Holsteinische Geest</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Schleswig-Holsteinisches Hügelland</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Nordwestliches Niedersachsen</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>Lüneburger Heide</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Westliches Niedersachsen</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>Hannover und Braunschweig</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>Teutoburger Wald</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Weser-Leine-Bergland</t>
+        </is>
+      </c>
+      <c r="L189" t="inlineStr"/>
+      <c r="M189" t="inlineStr"/>
+      <c r="N189" t="inlineStr"/>
+      <c r="O189" t="inlineStr"/>
+      <c r="P189" t="inlineStr"/>
+      <c r="Q189" t="inlineStr"/>
+      <c r="R189" t="inlineStr"/>
+      <c r="S189" t="inlineStr"/>
+      <c r="T189" t="inlineStr"/>
+      <c r="U189" t="inlineStr"/>
+      <c r="V189" t="inlineStr"/>
+      <c r="W189" t="inlineStr"/>
+      <c r="X189" t="inlineStr"/>
+      <c r="Y189" t="inlineStr"/>
+      <c r="Z189" t="inlineStr"/>
+      <c r="AA189" t="inlineStr"/>
+      <c r="AB189" t="inlineStr"/>
+      <c r="AC189" t="inlineStr"/>
+      <c r="AD189" t="inlineStr"/>
+      <c r="AE189" t="inlineStr"/>
+      <c r="AF189" t="inlineStr"/>
+      <c r="AG189" t="inlineStr"/>
+      <c r="AH189" t="inlineStr"/>
+      <c r="AI189" t="inlineStr"/>
+      <c r="AJ189" t="inlineStr"/>
+      <c r="AK189" t="inlineStr"/>
+      <c r="AL189" t="inlineStr"/>
+      <c r="AM189" t="inlineStr"/>
+      <c r="AN189" t="inlineStr"/>
+      <c r="AO189" t="inlineStr"/>
+      <c r="AP189" t="inlineStr"/>
+      <c r="AQ189" t="inlineStr"/>
+      <c r="AR189" t="inlineStr"/>
+      <c r="AS189" t="inlineStr"/>
+      <c r="AT189" t="inlineStr"/>
+      <c r="AU189" t="inlineStr"/>
+      <c r="AV189" t="inlineStr"/>
+      <c r="AW189" t="inlineStr"/>
+      <c r="AX189" t="inlineStr"/>
+      <c r="AY189" t="inlineStr"/>
+      <c r="AZ189" t="inlineStr"/>
+      <c r="BA189" t="inlineStr"/>
+      <c r="BB189" t="inlineStr"/>
+      <c r="BC189" t="inlineStr"/>
+      <c r="BD189" t="inlineStr"/>
+      <c r="BE189" t="inlineStr"/>
+      <c r="BF189" t="inlineStr"/>
+      <c r="BG189" t="inlineStr"/>
+      <c r="BH189" t="inlineStr"/>
+      <c r="BI189" t="inlineStr"/>
+      <c r="BJ189" t="inlineStr"/>
+      <c r="BK189" t="inlineStr"/>
+      <c r="BL189" t="inlineStr"/>
+      <c r="BM189" t="inlineStr"/>
+      <c r="BN189" t="inlineStr"/>
+      <c r="BO189" t="inlineStr"/>
+      <c r="BP189" t="inlineStr"/>
+      <c r="BQ189" t="inlineStr"/>
+      <c r="BR189" t="inlineStr"/>
+      <c r="BS189" t="inlineStr"/>
+      <c r="BT189" t="inlineStr"/>
+      <c r="BU189" t="inlineStr"/>
+      <c r="BV189" t="inlineStr"/>
+      <c r="BW189" t="inlineStr"/>
+      <c r="BX189" t="inlineStr"/>
+      <c r="BY189" t="inlineStr"/>
+      <c r="BZ189" t="inlineStr"/>
+      <c r="CA189" t="inlineStr"/>
+      <c r="CB189" t="inlineStr"/>
+      <c r="CC189" t="inlineStr"/>
+      <c r="CD189" t="inlineStr"/>
+      <c r="CE189" t="inlineStr"/>
+      <c r="CF189" t="inlineStr"/>
+      <c r="CG189" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gafor_log.xlsx
+++ b/data/gafor_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CG189"/>
+  <dimension ref="A1:CG190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25471,6 +25471,137 @@
       <c r="CF189" t="inlineStr"/>
       <c r="CG189" t="inlineStr"/>
     </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2026-09-28 08:00</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Ostfriesland</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Nordfriesland-Dithmarschen</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Schleswig-Holsteinische Geest</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Schleswig-Holsteinisches Hügelland</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Nordwestliches Niedersachsen</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Lüneburger Heide</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Westliches Niedersachsen</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>Hannover und Braunschweig</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>Teutoburger Wald</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Weser-Leine-Bergland</t>
+        </is>
+      </c>
+      <c r="L190" t="inlineStr"/>
+      <c r="M190" t="inlineStr"/>
+      <c r="N190" t="inlineStr"/>
+      <c r="O190" t="inlineStr"/>
+      <c r="P190" t="inlineStr"/>
+      <c r="Q190" t="inlineStr"/>
+      <c r="R190" t="inlineStr"/>
+      <c r="S190" t="inlineStr"/>
+      <c r="T190" t="inlineStr"/>
+      <c r="U190" t="inlineStr"/>
+      <c r="V190" t="inlineStr"/>
+      <c r="W190" t="inlineStr"/>
+      <c r="X190" t="inlineStr"/>
+      <c r="Y190" t="inlineStr"/>
+      <c r="Z190" t="inlineStr"/>
+      <c r="AA190" t="inlineStr"/>
+      <c r="AB190" t="inlineStr"/>
+      <c r="AC190" t="inlineStr"/>
+      <c r="AD190" t="inlineStr"/>
+      <c r="AE190" t="inlineStr"/>
+      <c r="AF190" t="inlineStr"/>
+      <c r="AG190" t="inlineStr"/>
+      <c r="AH190" t="inlineStr"/>
+      <c r="AI190" t="inlineStr"/>
+      <c r="AJ190" t="inlineStr"/>
+      <c r="AK190" t="inlineStr"/>
+      <c r="AL190" t="inlineStr"/>
+      <c r="AM190" t="inlineStr"/>
+      <c r="AN190" t="inlineStr"/>
+      <c r="AO190" t="inlineStr"/>
+      <c r="AP190" t="inlineStr"/>
+      <c r="AQ190" t="inlineStr"/>
+      <c r="AR190" t="inlineStr"/>
+      <c r="AS190" t="inlineStr"/>
+      <c r="AT190" t="inlineStr"/>
+      <c r="AU190" t="inlineStr"/>
+      <c r="AV190" t="inlineStr"/>
+      <c r="AW190" t="inlineStr"/>
+      <c r="AX190" t="inlineStr"/>
+      <c r="AY190" t="inlineStr"/>
+      <c r="AZ190" t="inlineStr"/>
+      <c r="BA190" t="inlineStr"/>
+      <c r="BB190" t="inlineStr"/>
+      <c r="BC190" t="inlineStr"/>
+      <c r="BD190" t="inlineStr"/>
+      <c r="BE190" t="inlineStr"/>
+      <c r="BF190" t="inlineStr"/>
+      <c r="BG190" t="inlineStr"/>
+      <c r="BH190" t="inlineStr"/>
+      <c r="BI190" t="inlineStr"/>
+      <c r="BJ190" t="inlineStr"/>
+      <c r="BK190" t="inlineStr"/>
+      <c r="BL190" t="inlineStr"/>
+      <c r="BM190" t="inlineStr"/>
+      <c r="BN190" t="inlineStr"/>
+      <c r="BO190" t="inlineStr"/>
+      <c r="BP190" t="inlineStr"/>
+      <c r="BQ190" t="inlineStr"/>
+      <c r="BR190" t="inlineStr"/>
+      <c r="BS190" t="inlineStr"/>
+      <c r="BT190" t="inlineStr"/>
+      <c r="BU190" t="inlineStr"/>
+      <c r="BV190" t="inlineStr"/>
+      <c r="BW190" t="inlineStr"/>
+      <c r="BX190" t="inlineStr"/>
+      <c r="BY190" t="inlineStr"/>
+      <c r="BZ190" t="inlineStr"/>
+      <c r="CA190" t="inlineStr"/>
+      <c r="CB190" t="inlineStr"/>
+      <c r="CC190" t="inlineStr"/>
+      <c r="CD190" t="inlineStr"/>
+      <c r="CE190" t="inlineStr"/>
+      <c r="CF190" t="inlineStr"/>
+      <c r="CG190" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gafor_log.xlsx
+++ b/data/gafor_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CG190"/>
+  <dimension ref="A1:CG191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25602,6 +25602,137 @@
       <c r="CF190" t="inlineStr"/>
       <c r="CG190" t="inlineStr"/>
     </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2026-09-29 08:00</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Ostfriesland</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Nordfriesland-Dithmarschen</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Schleswig-Holsteinische Geest</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Schleswig-Holsteinisches Hügelland</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>Nordwestliches Niedersachsen</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>Lüneburger Heide</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Westliches Niedersachsen</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>Hannover und Braunschweig</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>Teutoburger Wald</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Weser-Leine-Bergland</t>
+        </is>
+      </c>
+      <c r="L191" t="inlineStr"/>
+      <c r="M191" t="inlineStr"/>
+      <c r="N191" t="inlineStr"/>
+      <c r="O191" t="inlineStr"/>
+      <c r="P191" t="inlineStr"/>
+      <c r="Q191" t="inlineStr"/>
+      <c r="R191" t="inlineStr"/>
+      <c r="S191" t="inlineStr"/>
+      <c r="T191" t="inlineStr"/>
+      <c r="U191" t="inlineStr"/>
+      <c r="V191" t="inlineStr"/>
+      <c r="W191" t="inlineStr"/>
+      <c r="X191" t="inlineStr"/>
+      <c r="Y191" t="inlineStr"/>
+      <c r="Z191" t="inlineStr"/>
+      <c r="AA191" t="inlineStr"/>
+      <c r="AB191" t="inlineStr"/>
+      <c r="AC191" t="inlineStr"/>
+      <c r="AD191" t="inlineStr"/>
+      <c r="AE191" t="inlineStr"/>
+      <c r="AF191" t="inlineStr"/>
+      <c r="AG191" t="inlineStr"/>
+      <c r="AH191" t="inlineStr"/>
+      <c r="AI191" t="inlineStr"/>
+      <c r="AJ191" t="inlineStr"/>
+      <c r="AK191" t="inlineStr"/>
+      <c r="AL191" t="inlineStr"/>
+      <c r="AM191" t="inlineStr"/>
+      <c r="AN191" t="inlineStr"/>
+      <c r="AO191" t="inlineStr"/>
+      <c r="AP191" t="inlineStr"/>
+      <c r="AQ191" t="inlineStr"/>
+      <c r="AR191" t="inlineStr"/>
+      <c r="AS191" t="inlineStr"/>
+      <c r="AT191" t="inlineStr"/>
+      <c r="AU191" t="inlineStr"/>
+      <c r="AV191" t="inlineStr"/>
+      <c r="AW191" t="inlineStr"/>
+      <c r="AX191" t="inlineStr"/>
+      <c r="AY191" t="inlineStr"/>
+      <c r="AZ191" t="inlineStr"/>
+      <c r="BA191" t="inlineStr"/>
+      <c r="BB191" t="inlineStr"/>
+      <c r="BC191" t="inlineStr"/>
+      <c r="BD191" t="inlineStr"/>
+      <c r="BE191" t="inlineStr"/>
+      <c r="BF191" t="inlineStr"/>
+      <c r="BG191" t="inlineStr"/>
+      <c r="BH191" t="inlineStr"/>
+      <c r="BI191" t="inlineStr"/>
+      <c r="BJ191" t="inlineStr"/>
+      <c r="BK191" t="inlineStr"/>
+      <c r="BL191" t="inlineStr"/>
+      <c r="BM191" t="inlineStr"/>
+      <c r="BN191" t="inlineStr"/>
+      <c r="BO191" t="inlineStr"/>
+      <c r="BP191" t="inlineStr"/>
+      <c r="BQ191" t="inlineStr"/>
+      <c r="BR191" t="inlineStr"/>
+      <c r="BS191" t="inlineStr"/>
+      <c r="BT191" t="inlineStr"/>
+      <c r="BU191" t="inlineStr"/>
+      <c r="BV191" t="inlineStr"/>
+      <c r="BW191" t="inlineStr"/>
+      <c r="BX191" t="inlineStr"/>
+      <c r="BY191" t="inlineStr"/>
+      <c r="BZ191" t="inlineStr"/>
+      <c r="CA191" t="inlineStr"/>
+      <c r="CB191" t="inlineStr"/>
+      <c r="CC191" t="inlineStr"/>
+      <c r="CD191" t="inlineStr"/>
+      <c r="CE191" t="inlineStr"/>
+      <c r="CF191" t="inlineStr"/>
+      <c r="CG191" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gafor_log.xlsx
+++ b/data/gafor_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CG191"/>
+  <dimension ref="A1:CG192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25733,6 +25733,137 @@
       <c r="CF191" t="inlineStr"/>
       <c r="CG191" t="inlineStr"/>
     </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2026-09-30 08:00</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Ostfriesland</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Nordfriesland-Dithmarschen</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Schleswig-Holsteinische Geest</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Schleswig-Holsteinisches Hügelland</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>Nordwestliches Niedersachsen</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>Lüneburger Heide</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Westliches Niedersachsen</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>Hannover und Braunschweig</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>Teutoburger Wald</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Weser-Leine-Bergland</t>
+        </is>
+      </c>
+      <c r="L192" t="inlineStr"/>
+      <c r="M192" t="inlineStr"/>
+      <c r="N192" t="inlineStr"/>
+      <c r="O192" t="inlineStr"/>
+      <c r="P192" t="inlineStr"/>
+      <c r="Q192" t="inlineStr"/>
+      <c r="R192" t="inlineStr"/>
+      <c r="S192" t="inlineStr"/>
+      <c r="T192" t="inlineStr"/>
+      <c r="U192" t="inlineStr"/>
+      <c r="V192" t="inlineStr"/>
+      <c r="W192" t="inlineStr"/>
+      <c r="X192" t="inlineStr"/>
+      <c r="Y192" t="inlineStr"/>
+      <c r="Z192" t="inlineStr"/>
+      <c r="AA192" t="inlineStr"/>
+      <c r="AB192" t="inlineStr"/>
+      <c r="AC192" t="inlineStr"/>
+      <c r="AD192" t="inlineStr"/>
+      <c r="AE192" t="inlineStr"/>
+      <c r="AF192" t="inlineStr"/>
+      <c r="AG192" t="inlineStr"/>
+      <c r="AH192" t="inlineStr"/>
+      <c r="AI192" t="inlineStr"/>
+      <c r="AJ192" t="inlineStr"/>
+      <c r="AK192" t="inlineStr"/>
+      <c r="AL192" t="inlineStr"/>
+      <c r="AM192" t="inlineStr"/>
+      <c r="AN192" t="inlineStr"/>
+      <c r="AO192" t="inlineStr"/>
+      <c r="AP192" t="inlineStr"/>
+      <c r="AQ192" t="inlineStr"/>
+      <c r="AR192" t="inlineStr"/>
+      <c r="AS192" t="inlineStr"/>
+      <c r="AT192" t="inlineStr"/>
+      <c r="AU192" t="inlineStr"/>
+      <c r="AV192" t="inlineStr"/>
+      <c r="AW192" t="inlineStr"/>
+      <c r="AX192" t="inlineStr"/>
+      <c r="AY192" t="inlineStr"/>
+      <c r="AZ192" t="inlineStr"/>
+      <c r="BA192" t="inlineStr"/>
+      <c r="BB192" t="inlineStr"/>
+      <c r="BC192" t="inlineStr"/>
+      <c r="BD192" t="inlineStr"/>
+      <c r="BE192" t="inlineStr"/>
+      <c r="BF192" t="inlineStr"/>
+      <c r="BG192" t="inlineStr"/>
+      <c r="BH192" t="inlineStr"/>
+      <c r="BI192" t="inlineStr"/>
+      <c r="BJ192" t="inlineStr"/>
+      <c r="BK192" t="inlineStr"/>
+      <c r="BL192" t="inlineStr"/>
+      <c r="BM192" t="inlineStr"/>
+      <c r="BN192" t="inlineStr"/>
+      <c r="BO192" t="inlineStr"/>
+      <c r="BP192" t="inlineStr"/>
+      <c r="BQ192" t="inlineStr"/>
+      <c r="BR192" t="inlineStr"/>
+      <c r="BS192" t="inlineStr"/>
+      <c r="BT192" t="inlineStr"/>
+      <c r="BU192" t="inlineStr"/>
+      <c r="BV192" t="inlineStr"/>
+      <c r="BW192" t="inlineStr"/>
+      <c r="BX192" t="inlineStr"/>
+      <c r="BY192" t="inlineStr"/>
+      <c r="BZ192" t="inlineStr"/>
+      <c r="CA192" t="inlineStr"/>
+      <c r="CB192" t="inlineStr"/>
+      <c r="CC192" t="inlineStr"/>
+      <c r="CD192" t="inlineStr"/>
+      <c r="CE192" t="inlineStr"/>
+      <c r="CF192" t="inlineStr"/>
+      <c r="CG192" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gafor_log.xlsx
+++ b/data/gafor_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CG192"/>
+  <dimension ref="A1:CG193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25864,6 +25864,137 @@
       <c r="CF192" t="inlineStr"/>
       <c r="CG192" t="inlineStr"/>
     </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2026-10-01 08:00</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Ostfriesland</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Nordfriesland-Dithmarschen</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Schleswig-Holsteinische Geest</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Schleswig-Holsteinisches Hügelland</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>Nordwestliches Niedersachsen</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>Lüneburger Heide</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Westliches Niedersachsen</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>Hannover und Braunschweig</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>Teutoburger Wald</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Weser-Leine-Bergland</t>
+        </is>
+      </c>
+      <c r="L193" t="inlineStr"/>
+      <c r="M193" t="inlineStr"/>
+      <c r="N193" t="inlineStr"/>
+      <c r="O193" t="inlineStr"/>
+      <c r="P193" t="inlineStr"/>
+      <c r="Q193" t="inlineStr"/>
+      <c r="R193" t="inlineStr"/>
+      <c r="S193" t="inlineStr"/>
+      <c r="T193" t="inlineStr"/>
+      <c r="U193" t="inlineStr"/>
+      <c r="V193" t="inlineStr"/>
+      <c r="W193" t="inlineStr"/>
+      <c r="X193" t="inlineStr"/>
+      <c r="Y193" t="inlineStr"/>
+      <c r="Z193" t="inlineStr"/>
+      <c r="AA193" t="inlineStr"/>
+      <c r="AB193" t="inlineStr"/>
+      <c r="AC193" t="inlineStr"/>
+      <c r="AD193" t="inlineStr"/>
+      <c r="AE193" t="inlineStr"/>
+      <c r="AF193" t="inlineStr"/>
+      <c r="AG193" t="inlineStr"/>
+      <c r="AH193" t="inlineStr"/>
+      <c r="AI193" t="inlineStr"/>
+      <c r="AJ193" t="inlineStr"/>
+      <c r="AK193" t="inlineStr"/>
+      <c r="AL193" t="inlineStr"/>
+      <c r="AM193" t="inlineStr"/>
+      <c r="AN193" t="inlineStr"/>
+      <c r="AO193" t="inlineStr"/>
+      <c r="AP193" t="inlineStr"/>
+      <c r="AQ193" t="inlineStr"/>
+      <c r="AR193" t="inlineStr"/>
+      <c r="AS193" t="inlineStr"/>
+      <c r="AT193" t="inlineStr"/>
+      <c r="AU193" t="inlineStr"/>
+      <c r="AV193" t="inlineStr"/>
+      <c r="AW193" t="inlineStr"/>
+      <c r="AX193" t="inlineStr"/>
+      <c r="AY193" t="inlineStr"/>
+      <c r="AZ193" t="inlineStr"/>
+      <c r="BA193" t="inlineStr"/>
+      <c r="BB193" t="inlineStr"/>
+      <c r="BC193" t="inlineStr"/>
+      <c r="BD193" t="inlineStr"/>
+      <c r="BE193" t="inlineStr"/>
+      <c r="BF193" t="inlineStr"/>
+      <c r="BG193" t="inlineStr"/>
+      <c r="BH193" t="inlineStr"/>
+      <c r="BI193" t="inlineStr"/>
+      <c r="BJ193" t="inlineStr"/>
+      <c r="BK193" t="inlineStr"/>
+      <c r="BL193" t="inlineStr"/>
+      <c r="BM193" t="inlineStr"/>
+      <c r="BN193" t="inlineStr"/>
+      <c r="BO193" t="inlineStr"/>
+      <c r="BP193" t="inlineStr"/>
+      <c r="BQ193" t="inlineStr"/>
+      <c r="BR193" t="inlineStr"/>
+      <c r="BS193" t="inlineStr"/>
+      <c r="BT193" t="inlineStr"/>
+      <c r="BU193" t="inlineStr"/>
+      <c r="BV193" t="inlineStr"/>
+      <c r="BW193" t="inlineStr"/>
+      <c r="BX193" t="inlineStr"/>
+      <c r="BY193" t="inlineStr"/>
+      <c r="BZ193" t="inlineStr"/>
+      <c r="CA193" t="inlineStr"/>
+      <c r="CB193" t="inlineStr"/>
+      <c r="CC193" t="inlineStr"/>
+      <c r="CD193" t="inlineStr"/>
+      <c r="CE193" t="inlineStr"/>
+      <c r="CF193" t="inlineStr"/>
+      <c r="CG193" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gafor_log.xlsx
+++ b/data/gafor_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CG193"/>
+  <dimension ref="A1:CG194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25995,6 +25995,137 @@
       <c r="CF193" t="inlineStr"/>
       <c r="CG193" t="inlineStr"/>
     </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2026-10-03 08:00</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Ostfriesland</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Nordfriesland-Dithmarschen</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Schleswig-Holsteinische Geest</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Schleswig-Holsteinisches Hügelland</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>Nordwestliches Niedersachsen</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>Lüneburger Heide</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Westliches Niedersachsen</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>Hannover und Braunschweig</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>Teutoburger Wald</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Weser-Leine-Bergland</t>
+        </is>
+      </c>
+      <c r="L194" t="inlineStr"/>
+      <c r="M194" t="inlineStr"/>
+      <c r="N194" t="inlineStr"/>
+      <c r="O194" t="inlineStr"/>
+      <c r="P194" t="inlineStr"/>
+      <c r="Q194" t="inlineStr"/>
+      <c r="R194" t="inlineStr"/>
+      <c r="S194" t="inlineStr"/>
+      <c r="T194" t="inlineStr"/>
+      <c r="U194" t="inlineStr"/>
+      <c r="V194" t="inlineStr"/>
+      <c r="W194" t="inlineStr"/>
+      <c r="X194" t="inlineStr"/>
+      <c r="Y194" t="inlineStr"/>
+      <c r="Z194" t="inlineStr"/>
+      <c r="AA194" t="inlineStr"/>
+      <c r="AB194" t="inlineStr"/>
+      <c r="AC194" t="inlineStr"/>
+      <c r="AD194" t="inlineStr"/>
+      <c r="AE194" t="inlineStr"/>
+      <c r="AF194" t="inlineStr"/>
+      <c r="AG194" t="inlineStr"/>
+      <c r="AH194" t="inlineStr"/>
+      <c r="AI194" t="inlineStr"/>
+      <c r="AJ194" t="inlineStr"/>
+      <c r="AK194" t="inlineStr"/>
+      <c r="AL194" t="inlineStr"/>
+      <c r="AM194" t="inlineStr"/>
+      <c r="AN194" t="inlineStr"/>
+      <c r="AO194" t="inlineStr"/>
+      <c r="AP194" t="inlineStr"/>
+      <c r="AQ194" t="inlineStr"/>
+      <c r="AR194" t="inlineStr"/>
+      <c r="AS194" t="inlineStr"/>
+      <c r="AT194" t="inlineStr"/>
+      <c r="AU194" t="inlineStr"/>
+      <c r="AV194" t="inlineStr"/>
+      <c r="AW194" t="inlineStr"/>
+      <c r="AX194" t="inlineStr"/>
+      <c r="AY194" t="inlineStr"/>
+      <c r="AZ194" t="inlineStr"/>
+      <c r="BA194" t="inlineStr"/>
+      <c r="BB194" t="inlineStr"/>
+      <c r="BC194" t="inlineStr"/>
+      <c r="BD194" t="inlineStr"/>
+      <c r="BE194" t="inlineStr"/>
+      <c r="BF194" t="inlineStr"/>
+      <c r="BG194" t="inlineStr"/>
+      <c r="BH194" t="inlineStr"/>
+      <c r="BI194" t="inlineStr"/>
+      <c r="BJ194" t="inlineStr"/>
+      <c r="BK194" t="inlineStr"/>
+      <c r="BL194" t="inlineStr"/>
+      <c r="BM194" t="inlineStr"/>
+      <c r="BN194" t="inlineStr"/>
+      <c r="BO194" t="inlineStr"/>
+      <c r="BP194" t="inlineStr"/>
+      <c r="BQ194" t="inlineStr"/>
+      <c r="BR194" t="inlineStr"/>
+      <c r="BS194" t="inlineStr"/>
+      <c r="BT194" t="inlineStr"/>
+      <c r="BU194" t="inlineStr"/>
+      <c r="BV194" t="inlineStr"/>
+      <c r="BW194" t="inlineStr"/>
+      <c r="BX194" t="inlineStr"/>
+      <c r="BY194" t="inlineStr"/>
+      <c r="BZ194" t="inlineStr"/>
+      <c r="CA194" t="inlineStr"/>
+      <c r="CB194" t="inlineStr"/>
+      <c r="CC194" t="inlineStr"/>
+      <c r="CD194" t="inlineStr"/>
+      <c r="CE194" t="inlineStr"/>
+      <c r="CF194" t="inlineStr"/>
+      <c r="CG194" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gafor_log.xlsx
+++ b/data/gafor_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CG194"/>
+  <dimension ref="A1:CG195"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26126,6 +26126,137 @@
       <c r="CF194" t="inlineStr"/>
       <c r="CG194" t="inlineStr"/>
     </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2026-10-04 08:00</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Ostfriesland</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Nordfriesland-Dithmarschen</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Schleswig-Holsteinische Geest</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Schleswig-Holsteinisches Hügelland</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>Nordwestliches Niedersachsen</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>Lüneburger Heide</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Westliches Niedersachsen</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>Hannover und Braunschweig</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>Teutoburger Wald</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Weser-Leine-Bergland</t>
+        </is>
+      </c>
+      <c r="L195" t="inlineStr"/>
+      <c r="M195" t="inlineStr"/>
+      <c r="N195" t="inlineStr"/>
+      <c r="O195" t="inlineStr"/>
+      <c r="P195" t="inlineStr"/>
+      <c r="Q195" t="inlineStr"/>
+      <c r="R195" t="inlineStr"/>
+      <c r="S195" t="inlineStr"/>
+      <c r="T195" t="inlineStr"/>
+      <c r="U195" t="inlineStr"/>
+      <c r="V195" t="inlineStr"/>
+      <c r="W195" t="inlineStr"/>
+      <c r="X195" t="inlineStr"/>
+      <c r="Y195" t="inlineStr"/>
+      <c r="Z195" t="inlineStr"/>
+      <c r="AA195" t="inlineStr"/>
+      <c r="AB195" t="inlineStr"/>
+      <c r="AC195" t="inlineStr"/>
+      <c r="AD195" t="inlineStr"/>
+      <c r="AE195" t="inlineStr"/>
+      <c r="AF195" t="inlineStr"/>
+      <c r="AG195" t="inlineStr"/>
+      <c r="AH195" t="inlineStr"/>
+      <c r="AI195" t="inlineStr"/>
+      <c r="AJ195" t="inlineStr"/>
+      <c r="AK195" t="inlineStr"/>
+      <c r="AL195" t="inlineStr"/>
+      <c r="AM195" t="inlineStr"/>
+      <c r="AN195" t="inlineStr"/>
+      <c r="AO195" t="inlineStr"/>
+      <c r="AP195" t="inlineStr"/>
+      <c r="AQ195" t="inlineStr"/>
+      <c r="AR195" t="inlineStr"/>
+      <c r="AS195" t="inlineStr"/>
+      <c r="AT195" t="inlineStr"/>
+      <c r="AU195" t="inlineStr"/>
+      <c r="AV195" t="inlineStr"/>
+      <c r="AW195" t="inlineStr"/>
+      <c r="AX195" t="inlineStr"/>
+      <c r="AY195" t="inlineStr"/>
+      <c r="AZ195" t="inlineStr"/>
+      <c r="BA195" t="inlineStr"/>
+      <c r="BB195" t="inlineStr"/>
+      <c r="BC195" t="inlineStr"/>
+      <c r="BD195" t="inlineStr"/>
+      <c r="BE195" t="inlineStr"/>
+      <c r="BF195" t="inlineStr"/>
+      <c r="BG195" t="inlineStr"/>
+      <c r="BH195" t="inlineStr"/>
+      <c r="BI195" t="inlineStr"/>
+      <c r="BJ195" t="inlineStr"/>
+      <c r="BK195" t="inlineStr"/>
+      <c r="BL195" t="inlineStr"/>
+      <c r="BM195" t="inlineStr"/>
+      <c r="BN195" t="inlineStr"/>
+      <c r="BO195" t="inlineStr"/>
+      <c r="BP195" t="inlineStr"/>
+      <c r="BQ195" t="inlineStr"/>
+      <c r="BR195" t="inlineStr"/>
+      <c r="BS195" t="inlineStr"/>
+      <c r="BT195" t="inlineStr"/>
+      <c r="BU195" t="inlineStr"/>
+      <c r="BV195" t="inlineStr"/>
+      <c r="BW195" t="inlineStr"/>
+      <c r="BX195" t="inlineStr"/>
+      <c r="BY195" t="inlineStr"/>
+      <c r="BZ195" t="inlineStr"/>
+      <c r="CA195" t="inlineStr"/>
+      <c r="CB195" t="inlineStr"/>
+      <c r="CC195" t="inlineStr"/>
+      <c r="CD195" t="inlineStr"/>
+      <c r="CE195" t="inlineStr"/>
+      <c r="CF195" t="inlineStr"/>
+      <c r="CG195" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gafor_log.xlsx
+++ b/data/gafor_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CG195"/>
+  <dimension ref="A1:CG196"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26257,6 +26257,137 @@
       <c r="CF195" t="inlineStr"/>
       <c r="CG195" t="inlineStr"/>
     </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2026-10-05 08:00</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Ostfriesland</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Nordfriesland-Dithmarschen</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Schleswig-Holsteinische Geest</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Schleswig-Holsteinisches Hügelland</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>Nordwestliches Niedersachsen</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>Lüneburger Heide</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Westliches Niedersachsen</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>Hannover und Braunschweig</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>Teutoburger Wald</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Weser-Leine-Bergland</t>
+        </is>
+      </c>
+      <c r="L196" t="inlineStr"/>
+      <c r="M196" t="inlineStr"/>
+      <c r="N196" t="inlineStr"/>
+      <c r="O196" t="inlineStr"/>
+      <c r="P196" t="inlineStr"/>
+      <c r="Q196" t="inlineStr"/>
+      <c r="R196" t="inlineStr"/>
+      <c r="S196" t="inlineStr"/>
+      <c r="T196" t="inlineStr"/>
+      <c r="U196" t="inlineStr"/>
+      <c r="V196" t="inlineStr"/>
+      <c r="W196" t="inlineStr"/>
+      <c r="X196" t="inlineStr"/>
+      <c r="Y196" t="inlineStr"/>
+      <c r="Z196" t="inlineStr"/>
+      <c r="AA196" t="inlineStr"/>
+      <c r="AB196" t="inlineStr"/>
+      <c r="AC196" t="inlineStr"/>
+      <c r="AD196" t="inlineStr"/>
+      <c r="AE196" t="inlineStr"/>
+      <c r="AF196" t="inlineStr"/>
+      <c r="AG196" t="inlineStr"/>
+      <c r="AH196" t="inlineStr"/>
+      <c r="AI196" t="inlineStr"/>
+      <c r="AJ196" t="inlineStr"/>
+      <c r="AK196" t="inlineStr"/>
+      <c r="AL196" t="inlineStr"/>
+      <c r="AM196" t="inlineStr"/>
+      <c r="AN196" t="inlineStr"/>
+      <c r="AO196" t="inlineStr"/>
+      <c r="AP196" t="inlineStr"/>
+      <c r="AQ196" t="inlineStr"/>
+      <c r="AR196" t="inlineStr"/>
+      <c r="AS196" t="inlineStr"/>
+      <c r="AT196" t="inlineStr"/>
+      <c r="AU196" t="inlineStr"/>
+      <c r="AV196" t="inlineStr"/>
+      <c r="AW196" t="inlineStr"/>
+      <c r="AX196" t="inlineStr"/>
+      <c r="AY196" t="inlineStr"/>
+      <c r="AZ196" t="inlineStr"/>
+      <c r="BA196" t="inlineStr"/>
+      <c r="BB196" t="inlineStr"/>
+      <c r="BC196" t="inlineStr"/>
+      <c r="BD196" t="inlineStr"/>
+      <c r="BE196" t="inlineStr"/>
+      <c r="BF196" t="inlineStr"/>
+      <c r="BG196" t="inlineStr"/>
+      <c r="BH196" t="inlineStr"/>
+      <c r="BI196" t="inlineStr"/>
+      <c r="BJ196" t="inlineStr"/>
+      <c r="BK196" t="inlineStr"/>
+      <c r="BL196" t="inlineStr"/>
+      <c r="BM196" t="inlineStr"/>
+      <c r="BN196" t="inlineStr"/>
+      <c r="BO196" t="inlineStr"/>
+      <c r="BP196" t="inlineStr"/>
+      <c r="BQ196" t="inlineStr"/>
+      <c r="BR196" t="inlineStr"/>
+      <c r="BS196" t="inlineStr"/>
+      <c r="BT196" t="inlineStr"/>
+      <c r="BU196" t="inlineStr"/>
+      <c r="BV196" t="inlineStr"/>
+      <c r="BW196" t="inlineStr"/>
+      <c r="BX196" t="inlineStr"/>
+      <c r="BY196" t="inlineStr"/>
+      <c r="BZ196" t="inlineStr"/>
+      <c r="CA196" t="inlineStr"/>
+      <c r="CB196" t="inlineStr"/>
+      <c r="CC196" t="inlineStr"/>
+      <c r="CD196" t="inlineStr"/>
+      <c r="CE196" t="inlineStr"/>
+      <c r="CF196" t="inlineStr"/>
+      <c r="CG196" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gafor_log.xlsx
+++ b/data/gafor_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CG196"/>
+  <dimension ref="A1:CG197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26388,6 +26388,137 @@
       <c r="CF196" t="inlineStr"/>
       <c r="CG196" t="inlineStr"/>
     </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2026-10-06 08:00</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Ostfriesland</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Nordfriesland-Dithmarschen</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Schleswig-Holsteinische Geest</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Schleswig-Holsteinisches Hügelland</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>Nordwestliches Niedersachsen</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>Lüneburger Heide</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Westliches Niedersachsen</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>Hannover und Braunschweig</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>Teutoburger Wald</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Weser-Leine-Bergland</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr"/>
+      <c r="M197" t="inlineStr"/>
+      <c r="N197" t="inlineStr"/>
+      <c r="O197" t="inlineStr"/>
+      <c r="P197" t="inlineStr"/>
+      <c r="Q197" t="inlineStr"/>
+      <c r="R197" t="inlineStr"/>
+      <c r="S197" t="inlineStr"/>
+      <c r="T197" t="inlineStr"/>
+      <c r="U197" t="inlineStr"/>
+      <c r="V197" t="inlineStr"/>
+      <c r="W197" t="inlineStr"/>
+      <c r="X197" t="inlineStr"/>
+      <c r="Y197" t="inlineStr"/>
+      <c r="Z197" t="inlineStr"/>
+      <c r="AA197" t="inlineStr"/>
+      <c r="AB197" t="inlineStr"/>
+      <c r="AC197" t="inlineStr"/>
+      <c r="AD197" t="inlineStr"/>
+      <c r="AE197" t="inlineStr"/>
+      <c r="AF197" t="inlineStr"/>
+      <c r="AG197" t="inlineStr"/>
+      <c r="AH197" t="inlineStr"/>
+      <c r="AI197" t="inlineStr"/>
+      <c r="AJ197" t="inlineStr"/>
+      <c r="AK197" t="inlineStr"/>
+      <c r="AL197" t="inlineStr"/>
+      <c r="AM197" t="inlineStr"/>
+      <c r="AN197" t="inlineStr"/>
+      <c r="AO197" t="inlineStr"/>
+      <c r="AP197" t="inlineStr"/>
+      <c r="AQ197" t="inlineStr"/>
+      <c r="AR197" t="inlineStr"/>
+      <c r="AS197" t="inlineStr"/>
+      <c r="AT197" t="inlineStr"/>
+      <c r="AU197" t="inlineStr"/>
+      <c r="AV197" t="inlineStr"/>
+      <c r="AW197" t="inlineStr"/>
+      <c r="AX197" t="inlineStr"/>
+      <c r="AY197" t="inlineStr"/>
+      <c r="AZ197" t="inlineStr"/>
+      <c r="BA197" t="inlineStr"/>
+      <c r="BB197" t="inlineStr"/>
+      <c r="BC197" t="inlineStr"/>
+      <c r="BD197" t="inlineStr"/>
+      <c r="BE197" t="inlineStr"/>
+      <c r="BF197" t="inlineStr"/>
+      <c r="BG197" t="inlineStr"/>
+      <c r="BH197" t="inlineStr"/>
+      <c r="BI197" t="inlineStr"/>
+      <c r="BJ197" t="inlineStr"/>
+      <c r="BK197" t="inlineStr"/>
+      <c r="BL197" t="inlineStr"/>
+      <c r="BM197" t="inlineStr"/>
+      <c r="BN197" t="inlineStr"/>
+      <c r="BO197" t="inlineStr"/>
+      <c r="BP197" t="inlineStr"/>
+      <c r="BQ197" t="inlineStr"/>
+      <c r="BR197" t="inlineStr"/>
+      <c r="BS197" t="inlineStr"/>
+      <c r="BT197" t="inlineStr"/>
+      <c r="BU197" t="inlineStr"/>
+      <c r="BV197" t="inlineStr"/>
+      <c r="BW197" t="inlineStr"/>
+      <c r="BX197" t="inlineStr"/>
+      <c r="BY197" t="inlineStr"/>
+      <c r="BZ197" t="inlineStr"/>
+      <c r="CA197" t="inlineStr"/>
+      <c r="CB197" t="inlineStr"/>
+      <c r="CC197" t="inlineStr"/>
+      <c r="CD197" t="inlineStr"/>
+      <c r="CE197" t="inlineStr"/>
+      <c r="CF197" t="inlineStr"/>
+      <c r="CG197" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gafor_log.xlsx
+++ b/data/gafor_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CG197"/>
+  <dimension ref="A1:CG198"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26519,6 +26519,137 @@
       <c r="CF197" t="inlineStr"/>
       <c r="CG197" t="inlineStr"/>
     </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2026-10-08 08:00</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Ostfriesland</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Nordfriesland-Dithmarschen</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Schleswig-Holsteinische Geest</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Schleswig-Holsteinisches Hügelland</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>Nordwestliches Niedersachsen</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>Lüneburger Heide</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>Westliches Niedersachsen</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>Hannover und Braunschweig</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>Teutoburger Wald</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Weser-Leine-Bergland</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr"/>
+      <c r="M198" t="inlineStr"/>
+      <c r="N198" t="inlineStr"/>
+      <c r="O198" t="inlineStr"/>
+      <c r="P198" t="inlineStr"/>
+      <c r="Q198" t="inlineStr"/>
+      <c r="R198" t="inlineStr"/>
+      <c r="S198" t="inlineStr"/>
+      <c r="T198" t="inlineStr"/>
+      <c r="U198" t="inlineStr"/>
+      <c r="V198" t="inlineStr"/>
+      <c r="W198" t="inlineStr"/>
+      <c r="X198" t="inlineStr"/>
+      <c r="Y198" t="inlineStr"/>
+      <c r="Z198" t="inlineStr"/>
+      <c r="AA198" t="inlineStr"/>
+      <c r="AB198" t="inlineStr"/>
+      <c r="AC198" t="inlineStr"/>
+      <c r="AD198" t="inlineStr"/>
+      <c r="AE198" t="inlineStr"/>
+      <c r="AF198" t="inlineStr"/>
+      <c r="AG198" t="inlineStr"/>
+      <c r="AH198" t="inlineStr"/>
+      <c r="AI198" t="inlineStr"/>
+      <c r="AJ198" t="inlineStr"/>
+      <c r="AK198" t="inlineStr"/>
+      <c r="AL198" t="inlineStr"/>
+      <c r="AM198" t="inlineStr"/>
+      <c r="AN198" t="inlineStr"/>
+      <c r="AO198" t="inlineStr"/>
+      <c r="AP198" t="inlineStr"/>
+      <c r="AQ198" t="inlineStr"/>
+      <c r="AR198" t="inlineStr"/>
+      <c r="AS198" t="inlineStr"/>
+      <c r="AT198" t="inlineStr"/>
+      <c r="AU198" t="inlineStr"/>
+      <c r="AV198" t="inlineStr"/>
+      <c r="AW198" t="inlineStr"/>
+      <c r="AX198" t="inlineStr"/>
+      <c r="AY198" t="inlineStr"/>
+      <c r="AZ198" t="inlineStr"/>
+      <c r="BA198" t="inlineStr"/>
+      <c r="BB198" t="inlineStr"/>
+      <c r="BC198" t="inlineStr"/>
+      <c r="BD198" t="inlineStr"/>
+      <c r="BE198" t="inlineStr"/>
+      <c r="BF198" t="inlineStr"/>
+      <c r="BG198" t="inlineStr"/>
+      <c r="BH198" t="inlineStr"/>
+      <c r="BI198" t="inlineStr"/>
+      <c r="BJ198" t="inlineStr"/>
+      <c r="BK198" t="inlineStr"/>
+      <c r="BL198" t="inlineStr"/>
+      <c r="BM198" t="inlineStr"/>
+      <c r="BN198" t="inlineStr"/>
+      <c r="BO198" t="inlineStr"/>
+      <c r="BP198" t="inlineStr"/>
+      <c r="BQ198" t="inlineStr"/>
+      <c r="BR198" t="inlineStr"/>
+      <c r="BS198" t="inlineStr"/>
+      <c r="BT198" t="inlineStr"/>
+      <c r="BU198" t="inlineStr"/>
+      <c r="BV198" t="inlineStr"/>
+      <c r="BW198" t="inlineStr"/>
+      <c r="BX198" t="inlineStr"/>
+      <c r="BY198" t="inlineStr"/>
+      <c r="BZ198" t="inlineStr"/>
+      <c r="CA198" t="inlineStr"/>
+      <c r="CB198" t="inlineStr"/>
+      <c r="CC198" t="inlineStr"/>
+      <c r="CD198" t="inlineStr"/>
+      <c r="CE198" t="inlineStr"/>
+      <c r="CF198" t="inlineStr"/>
+      <c r="CG198" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gafor_log.xlsx
+++ b/data/gafor_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CG198"/>
+  <dimension ref="A1:CG199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26650,6 +26650,137 @@
       <c r="CF198" t="inlineStr"/>
       <c r="CG198" t="inlineStr"/>
     </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2026-10-09 08:00</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Ostfriesland</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Nordfriesland-Dithmarschen</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Schleswig-Holsteinische Geest</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Schleswig-Holsteinisches Hügelland</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>Nordwestliches Niedersachsen</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>Lüneburger Heide</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>Westliches Niedersachsen</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>Hannover und Braunschweig</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>Teutoburger Wald</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Weser-Leine-Bergland</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr"/>
+      <c r="M199" t="inlineStr"/>
+      <c r="N199" t="inlineStr"/>
+      <c r="O199" t="inlineStr"/>
+      <c r="P199" t="inlineStr"/>
+      <c r="Q199" t="inlineStr"/>
+      <c r="R199" t="inlineStr"/>
+      <c r="S199" t="inlineStr"/>
+      <c r="T199" t="inlineStr"/>
+      <c r="U199" t="inlineStr"/>
+      <c r="V199" t="inlineStr"/>
+      <c r="W199" t="inlineStr"/>
+      <c r="X199" t="inlineStr"/>
+      <c r="Y199" t="inlineStr"/>
+      <c r="Z199" t="inlineStr"/>
+      <c r="AA199" t="inlineStr"/>
+      <c r="AB199" t="inlineStr"/>
+      <c r="AC199" t="inlineStr"/>
+      <c r="AD199" t="inlineStr"/>
+      <c r="AE199" t="inlineStr"/>
+      <c r="AF199" t="inlineStr"/>
+      <c r="AG199" t="inlineStr"/>
+      <c r="AH199" t="inlineStr"/>
+      <c r="AI199" t="inlineStr"/>
+      <c r="AJ199" t="inlineStr"/>
+      <c r="AK199" t="inlineStr"/>
+      <c r="AL199" t="inlineStr"/>
+      <c r="AM199" t="inlineStr"/>
+      <c r="AN199" t="inlineStr"/>
+      <c r="AO199" t="inlineStr"/>
+      <c r="AP199" t="inlineStr"/>
+      <c r="AQ199" t="inlineStr"/>
+      <c r="AR199" t="inlineStr"/>
+      <c r="AS199" t="inlineStr"/>
+      <c r="AT199" t="inlineStr"/>
+      <c r="AU199" t="inlineStr"/>
+      <c r="AV199" t="inlineStr"/>
+      <c r="AW199" t="inlineStr"/>
+      <c r="AX199" t="inlineStr"/>
+      <c r="AY199" t="inlineStr"/>
+      <c r="AZ199" t="inlineStr"/>
+      <c r="BA199" t="inlineStr"/>
+      <c r="BB199" t="inlineStr"/>
+      <c r="BC199" t="inlineStr"/>
+      <c r="BD199" t="inlineStr"/>
+      <c r="BE199" t="inlineStr"/>
+      <c r="BF199" t="inlineStr"/>
+      <c r="BG199" t="inlineStr"/>
+      <c r="BH199" t="inlineStr"/>
+      <c r="BI199" t="inlineStr"/>
+      <c r="BJ199" t="inlineStr"/>
+      <c r="BK199" t="inlineStr"/>
+      <c r="BL199" t="inlineStr"/>
+      <c r="BM199" t="inlineStr"/>
+      <c r="BN199" t="inlineStr"/>
+      <c r="BO199" t="inlineStr"/>
+      <c r="BP199" t="inlineStr"/>
+      <c r="BQ199" t="inlineStr"/>
+      <c r="BR199" t="inlineStr"/>
+      <c r="BS199" t="inlineStr"/>
+      <c r="BT199" t="inlineStr"/>
+      <c r="BU199" t="inlineStr"/>
+      <c r="BV199" t="inlineStr"/>
+      <c r="BW199" t="inlineStr"/>
+      <c r="BX199" t="inlineStr"/>
+      <c r="BY199" t="inlineStr"/>
+      <c r="BZ199" t="inlineStr"/>
+      <c r="CA199" t="inlineStr"/>
+      <c r="CB199" t="inlineStr"/>
+      <c r="CC199" t="inlineStr"/>
+      <c r="CD199" t="inlineStr"/>
+      <c r="CE199" t="inlineStr"/>
+      <c r="CF199" t="inlineStr"/>
+      <c r="CG199" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gafor_log.xlsx
+++ b/data/gafor_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CG199"/>
+  <dimension ref="A1:CG200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26781,6 +26781,137 @@
       <c r="CF199" t="inlineStr"/>
       <c r="CG199" t="inlineStr"/>
     </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2026-10-12 08:00</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Ostfriesland</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Nordfriesland-Dithmarschen</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Schleswig-Holsteinische Geest</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Schleswig-Holsteinisches Hügelland</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>Nordwestliches Niedersachsen</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>Lüneburger Heide</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Westliches Niedersachsen</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>Hannover und Braunschweig</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>Teutoburger Wald</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Weser-Leine-Bergland</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr"/>
+      <c r="M200" t="inlineStr"/>
+      <c r="N200" t="inlineStr"/>
+      <c r="O200" t="inlineStr"/>
+      <c r="P200" t="inlineStr"/>
+      <c r="Q200" t="inlineStr"/>
+      <c r="R200" t="inlineStr"/>
+      <c r="S200" t="inlineStr"/>
+      <c r="T200" t="inlineStr"/>
+      <c r="U200" t="inlineStr"/>
+      <c r="V200" t="inlineStr"/>
+      <c r="W200" t="inlineStr"/>
+      <c r="X200" t="inlineStr"/>
+      <c r="Y200" t="inlineStr"/>
+      <c r="Z200" t="inlineStr"/>
+      <c r="AA200" t="inlineStr"/>
+      <c r="AB200" t="inlineStr"/>
+      <c r="AC200" t="inlineStr"/>
+      <c r="AD200" t="inlineStr"/>
+      <c r="AE200" t="inlineStr"/>
+      <c r="AF200" t="inlineStr"/>
+      <c r="AG200" t="inlineStr"/>
+      <c r="AH200" t="inlineStr"/>
+      <c r="AI200" t="inlineStr"/>
+      <c r="AJ200" t="inlineStr"/>
+      <c r="AK200" t="inlineStr"/>
+      <c r="AL200" t="inlineStr"/>
+      <c r="AM200" t="inlineStr"/>
+      <c r="AN200" t="inlineStr"/>
+      <c r="AO200" t="inlineStr"/>
+      <c r="AP200" t="inlineStr"/>
+      <c r="AQ200" t="inlineStr"/>
+      <c r="AR200" t="inlineStr"/>
+      <c r="AS200" t="inlineStr"/>
+      <c r="AT200" t="inlineStr"/>
+      <c r="AU200" t="inlineStr"/>
+      <c r="AV200" t="inlineStr"/>
+      <c r="AW200" t="inlineStr"/>
+      <c r="AX200" t="inlineStr"/>
+      <c r="AY200" t="inlineStr"/>
+      <c r="AZ200" t="inlineStr"/>
+      <c r="BA200" t="inlineStr"/>
+      <c r="BB200" t="inlineStr"/>
+      <c r="BC200" t="inlineStr"/>
+      <c r="BD200" t="inlineStr"/>
+      <c r="BE200" t="inlineStr"/>
+      <c r="BF200" t="inlineStr"/>
+      <c r="BG200" t="inlineStr"/>
+      <c r="BH200" t="inlineStr"/>
+      <c r="BI200" t="inlineStr"/>
+      <c r="BJ200" t="inlineStr"/>
+      <c r="BK200" t="inlineStr"/>
+      <c r="BL200" t="inlineStr"/>
+      <c r="BM200" t="inlineStr"/>
+      <c r="BN200" t="inlineStr"/>
+      <c r="BO200" t="inlineStr"/>
+      <c r="BP200" t="inlineStr"/>
+      <c r="BQ200" t="inlineStr"/>
+      <c r="BR200" t="inlineStr"/>
+      <c r="BS200" t="inlineStr"/>
+      <c r="BT200" t="inlineStr"/>
+      <c r="BU200" t="inlineStr"/>
+      <c r="BV200" t="inlineStr"/>
+      <c r="BW200" t="inlineStr"/>
+      <c r="BX200" t="inlineStr"/>
+      <c r="BY200" t="inlineStr"/>
+      <c r="BZ200" t="inlineStr"/>
+      <c r="CA200" t="inlineStr"/>
+      <c r="CB200" t="inlineStr"/>
+      <c r="CC200" t="inlineStr"/>
+      <c r="CD200" t="inlineStr"/>
+      <c r="CE200" t="inlineStr"/>
+      <c r="CF200" t="inlineStr"/>
+      <c r="CG200" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gafor_log.xlsx
+++ b/data/gafor_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CG200"/>
+  <dimension ref="A1:CG201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26912,6 +26912,137 @@
       <c r="CF200" t="inlineStr"/>
       <c r="CG200" t="inlineStr"/>
     </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2026-10-13 08:00</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Ostfriesland</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Nordfriesland-Dithmarschen</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Schleswig-Holsteinische Geest</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Schleswig-Holsteinisches Hügelland</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>Nordwestliches Niedersachsen</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>Lüneburger Heide</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Westliches Niedersachsen</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>Hannover und Braunschweig</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>Teutoburger Wald</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Weser-Leine-Bergland</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr"/>
+      <c r="M201" t="inlineStr"/>
+      <c r="N201" t="inlineStr"/>
+      <c r="O201" t="inlineStr"/>
+      <c r="P201" t="inlineStr"/>
+      <c r="Q201" t="inlineStr"/>
+      <c r="R201" t="inlineStr"/>
+      <c r="S201" t="inlineStr"/>
+      <c r="T201" t="inlineStr"/>
+      <c r="U201" t="inlineStr"/>
+      <c r="V201" t="inlineStr"/>
+      <c r="W201" t="inlineStr"/>
+      <c r="X201" t="inlineStr"/>
+      <c r="Y201" t="inlineStr"/>
+      <c r="Z201" t="inlineStr"/>
+      <c r="AA201" t="inlineStr"/>
+      <c r="AB201" t="inlineStr"/>
+      <c r="AC201" t="inlineStr"/>
+      <c r="AD201" t="inlineStr"/>
+      <c r="AE201" t="inlineStr"/>
+      <c r="AF201" t="inlineStr"/>
+      <c r="AG201" t="inlineStr"/>
+      <c r="AH201" t="inlineStr"/>
+      <c r="AI201" t="inlineStr"/>
+      <c r="AJ201" t="inlineStr"/>
+      <c r="AK201" t="inlineStr"/>
+      <c r="AL201" t="inlineStr"/>
+      <c r="AM201" t="inlineStr"/>
+      <c r="AN201" t="inlineStr"/>
+      <c r="AO201" t="inlineStr"/>
+      <c r="AP201" t="inlineStr"/>
+      <c r="AQ201" t="inlineStr"/>
+      <c r="AR201" t="inlineStr"/>
+      <c r="AS201" t="inlineStr"/>
+      <c r="AT201" t="inlineStr"/>
+      <c r="AU201" t="inlineStr"/>
+      <c r="AV201" t="inlineStr"/>
+      <c r="AW201" t="inlineStr"/>
+      <c r="AX201" t="inlineStr"/>
+      <c r="AY201" t="inlineStr"/>
+      <c r="AZ201" t="inlineStr"/>
+      <c r="BA201" t="inlineStr"/>
+      <c r="BB201" t="inlineStr"/>
+      <c r="BC201" t="inlineStr"/>
+      <c r="BD201" t="inlineStr"/>
+      <c r="BE201" t="inlineStr"/>
+      <c r="BF201" t="inlineStr"/>
+      <c r="BG201" t="inlineStr"/>
+      <c r="BH201" t="inlineStr"/>
+      <c r="BI201" t="inlineStr"/>
+      <c r="BJ201" t="inlineStr"/>
+      <c r="BK201" t="inlineStr"/>
+      <c r="BL201" t="inlineStr"/>
+      <c r="BM201" t="inlineStr"/>
+      <c r="BN201" t="inlineStr"/>
+      <c r="BO201" t="inlineStr"/>
+      <c r="BP201" t="inlineStr"/>
+      <c r="BQ201" t="inlineStr"/>
+      <c r="BR201" t="inlineStr"/>
+      <c r="BS201" t="inlineStr"/>
+      <c r="BT201" t="inlineStr"/>
+      <c r="BU201" t="inlineStr"/>
+      <c r="BV201" t="inlineStr"/>
+      <c r="BW201" t="inlineStr"/>
+      <c r="BX201" t="inlineStr"/>
+      <c r="BY201" t="inlineStr"/>
+      <c r="BZ201" t="inlineStr"/>
+      <c r="CA201" t="inlineStr"/>
+      <c r="CB201" t="inlineStr"/>
+      <c r="CC201" t="inlineStr"/>
+      <c r="CD201" t="inlineStr"/>
+      <c r="CE201" t="inlineStr"/>
+      <c r="CF201" t="inlineStr"/>
+      <c r="CG201" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gafor_log.xlsx
+++ b/data/gafor_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CG201"/>
+  <dimension ref="A1:CG202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27043,6 +27043,137 @@
       <c r="CF201" t="inlineStr"/>
       <c r="CG201" t="inlineStr"/>
     </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2026-10-14 08:00</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Ostfriesland</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Nordfriesland-Dithmarschen</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Schleswig-Holsteinische Geest</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Schleswig-Holsteinisches Hügelland</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>Nordwestliches Niedersachsen</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>Lüneburger Heide</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Westliches Niedersachsen</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>Hannover und Braunschweig</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>Teutoburger Wald</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Weser-Leine-Bergland</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr"/>
+      <c r="M202" t="inlineStr"/>
+      <c r="N202" t="inlineStr"/>
+      <c r="O202" t="inlineStr"/>
+      <c r="P202" t="inlineStr"/>
+      <c r="Q202" t="inlineStr"/>
+      <c r="R202" t="inlineStr"/>
+      <c r="S202" t="inlineStr"/>
+      <c r="T202" t="inlineStr"/>
+      <c r="U202" t="inlineStr"/>
+      <c r="V202" t="inlineStr"/>
+      <c r="W202" t="inlineStr"/>
+      <c r="X202" t="inlineStr"/>
+      <c r="Y202" t="inlineStr"/>
+      <c r="Z202" t="inlineStr"/>
+      <c r="AA202" t="inlineStr"/>
+      <c r="AB202" t="inlineStr"/>
+      <c r="AC202" t="inlineStr"/>
+      <c r="AD202" t="inlineStr"/>
+      <c r="AE202" t="inlineStr"/>
+      <c r="AF202" t="inlineStr"/>
+      <c r="AG202" t="inlineStr"/>
+      <c r="AH202" t="inlineStr"/>
+      <c r="AI202" t="inlineStr"/>
+      <c r="AJ202" t="inlineStr"/>
+      <c r="AK202" t="inlineStr"/>
+      <c r="AL202" t="inlineStr"/>
+      <c r="AM202" t="inlineStr"/>
+      <c r="AN202" t="inlineStr"/>
+      <c r="AO202" t="inlineStr"/>
+      <c r="AP202" t="inlineStr"/>
+      <c r="AQ202" t="inlineStr"/>
+      <c r="AR202" t="inlineStr"/>
+      <c r="AS202" t="inlineStr"/>
+      <c r="AT202" t="inlineStr"/>
+      <c r="AU202" t="inlineStr"/>
+      <c r="AV202" t="inlineStr"/>
+      <c r="AW202" t="inlineStr"/>
+      <c r="AX202" t="inlineStr"/>
+      <c r="AY202" t="inlineStr"/>
+      <c r="AZ202" t="inlineStr"/>
+      <c r="BA202" t="inlineStr"/>
+      <c r="BB202" t="inlineStr"/>
+      <c r="BC202" t="inlineStr"/>
+      <c r="BD202" t="inlineStr"/>
+      <c r="BE202" t="inlineStr"/>
+      <c r="BF202" t="inlineStr"/>
+      <c r="BG202" t="inlineStr"/>
+      <c r="BH202" t="inlineStr"/>
+      <c r="BI202" t="inlineStr"/>
+      <c r="BJ202" t="inlineStr"/>
+      <c r="BK202" t="inlineStr"/>
+      <c r="BL202" t="inlineStr"/>
+      <c r="BM202" t="inlineStr"/>
+      <c r="BN202" t="inlineStr"/>
+      <c r="BO202" t="inlineStr"/>
+      <c r="BP202" t="inlineStr"/>
+      <c r="BQ202" t="inlineStr"/>
+      <c r="BR202" t="inlineStr"/>
+      <c r="BS202" t="inlineStr"/>
+      <c r="BT202" t="inlineStr"/>
+      <c r="BU202" t="inlineStr"/>
+      <c r="BV202" t="inlineStr"/>
+      <c r="BW202" t="inlineStr"/>
+      <c r="BX202" t="inlineStr"/>
+      <c r="BY202" t="inlineStr"/>
+      <c r="BZ202" t="inlineStr"/>
+      <c r="CA202" t="inlineStr"/>
+      <c r="CB202" t="inlineStr"/>
+      <c r="CC202" t="inlineStr"/>
+      <c r="CD202" t="inlineStr"/>
+      <c r="CE202" t="inlineStr"/>
+      <c r="CF202" t="inlineStr"/>
+      <c r="CG202" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gafor_log.xlsx
+++ b/data/gafor_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CG202"/>
+  <dimension ref="A1:CG203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27174,6 +27174,137 @@
       <c r="CF202" t="inlineStr"/>
       <c r="CG202" t="inlineStr"/>
     </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2026-10-15 08:00</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Ostfriesland</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Nordfriesland-Dithmarschen</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Schleswig-Holsteinische Geest</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>Schleswig-Holsteinisches Hügelland</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>Nordwestliches Niedersachsen</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>Lüneburger Heide</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Westliches Niedersachsen</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>Hannover und Braunschweig</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>Teutoburger Wald</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Weser-Leine-Bergland</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr"/>
+      <c r="M203" t="inlineStr"/>
+      <c r="N203" t="inlineStr"/>
+      <c r="O203" t="inlineStr"/>
+      <c r="P203" t="inlineStr"/>
+      <c r="Q203" t="inlineStr"/>
+      <c r="R203" t="inlineStr"/>
+      <c r="S203" t="inlineStr"/>
+      <c r="T203" t="inlineStr"/>
+      <c r="U203" t="inlineStr"/>
+      <c r="V203" t="inlineStr"/>
+      <c r="W203" t="inlineStr"/>
+      <c r="X203" t="inlineStr"/>
+      <c r="Y203" t="inlineStr"/>
+      <c r="Z203" t="inlineStr"/>
+      <c r="AA203" t="inlineStr"/>
+      <c r="AB203" t="inlineStr"/>
+      <c r="AC203" t="inlineStr"/>
+      <c r="AD203" t="inlineStr"/>
+      <c r="AE203" t="inlineStr"/>
+      <c r="AF203" t="inlineStr"/>
+      <c r="AG203" t="inlineStr"/>
+      <c r="AH203" t="inlineStr"/>
+      <c r="AI203" t="inlineStr"/>
+      <c r="AJ203" t="inlineStr"/>
+      <c r="AK203" t="inlineStr"/>
+      <c r="AL203" t="inlineStr"/>
+      <c r="AM203" t="inlineStr"/>
+      <c r="AN203" t="inlineStr"/>
+      <c r="AO203" t="inlineStr"/>
+      <c r="AP203" t="inlineStr"/>
+      <c r="AQ203" t="inlineStr"/>
+      <c r="AR203" t="inlineStr"/>
+      <c r="AS203" t="inlineStr"/>
+      <c r="AT203" t="inlineStr"/>
+      <c r="AU203" t="inlineStr"/>
+      <c r="AV203" t="inlineStr"/>
+      <c r="AW203" t="inlineStr"/>
+      <c r="AX203" t="inlineStr"/>
+      <c r="AY203" t="inlineStr"/>
+      <c r="AZ203" t="inlineStr"/>
+      <c r="BA203" t="inlineStr"/>
+      <c r="BB203" t="inlineStr"/>
+      <c r="BC203" t="inlineStr"/>
+      <c r="BD203" t="inlineStr"/>
+      <c r="BE203" t="inlineStr"/>
+      <c r="BF203" t="inlineStr"/>
+      <c r="BG203" t="inlineStr"/>
+      <c r="BH203" t="inlineStr"/>
+      <c r="BI203" t="inlineStr"/>
+      <c r="BJ203" t="inlineStr"/>
+      <c r="BK203" t="inlineStr"/>
+      <c r="BL203" t="inlineStr"/>
+      <c r="BM203" t="inlineStr"/>
+      <c r="BN203" t="inlineStr"/>
+      <c r="BO203" t="inlineStr"/>
+      <c r="BP203" t="inlineStr"/>
+      <c r="BQ203" t="inlineStr"/>
+      <c r="BR203" t="inlineStr"/>
+      <c r="BS203" t="inlineStr"/>
+      <c r="BT203" t="inlineStr"/>
+      <c r="BU203" t="inlineStr"/>
+      <c r="BV203" t="inlineStr"/>
+      <c r="BW203" t="inlineStr"/>
+      <c r="BX203" t="inlineStr"/>
+      <c r="BY203" t="inlineStr"/>
+      <c r="BZ203" t="inlineStr"/>
+      <c r="CA203" t="inlineStr"/>
+      <c r="CB203" t="inlineStr"/>
+      <c r="CC203" t="inlineStr"/>
+      <c r="CD203" t="inlineStr"/>
+      <c r="CE203" t="inlineStr"/>
+      <c r="CF203" t="inlineStr"/>
+      <c r="CG203" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gafor_log.xlsx
+++ b/data/gafor_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CG203"/>
+  <dimension ref="A1:CG204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27305,6 +27305,137 @@
       <c r="CF203" t="inlineStr"/>
       <c r="CG203" t="inlineStr"/>
     </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2026-10-17 08:00</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Ostfriesland</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Nordfriesland-Dithmarschen</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Schleswig-Holsteinische Geest</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Schleswig-Holsteinisches Hügelland</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>Nordwestliches Niedersachsen</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>Lüneburger Heide</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Westliches Niedersachsen</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>Hannover und Braunschweig</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>Teutoburger Wald</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Weser-Leine-Bergland</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr"/>
+      <c r="M204" t="inlineStr"/>
+      <c r="N204" t="inlineStr"/>
+      <c r="O204" t="inlineStr"/>
+      <c r="P204" t="inlineStr"/>
+      <c r="Q204" t="inlineStr"/>
+      <c r="R204" t="inlineStr"/>
+      <c r="S204" t="inlineStr"/>
+      <c r="T204" t="inlineStr"/>
+      <c r="U204" t="inlineStr"/>
+      <c r="V204" t="inlineStr"/>
+      <c r="W204" t="inlineStr"/>
+      <c r="X204" t="inlineStr"/>
+      <c r="Y204" t="inlineStr"/>
+      <c r="Z204" t="inlineStr"/>
+      <c r="AA204" t="inlineStr"/>
+      <c r="AB204" t="inlineStr"/>
+      <c r="AC204" t="inlineStr"/>
+      <c r="AD204" t="inlineStr"/>
+      <c r="AE204" t="inlineStr"/>
+      <c r="AF204" t="inlineStr"/>
+      <c r="AG204" t="inlineStr"/>
+      <c r="AH204" t="inlineStr"/>
+      <c r="AI204" t="inlineStr"/>
+      <c r="AJ204" t="inlineStr"/>
+      <c r="AK204" t="inlineStr"/>
+      <c r="AL204" t="inlineStr"/>
+      <c r="AM204" t="inlineStr"/>
+      <c r="AN204" t="inlineStr"/>
+      <c r="AO204" t="inlineStr"/>
+      <c r="AP204" t="inlineStr"/>
+      <c r="AQ204" t="inlineStr"/>
+      <c r="AR204" t="inlineStr"/>
+      <c r="AS204" t="inlineStr"/>
+      <c r="AT204" t="inlineStr"/>
+      <c r="AU204" t="inlineStr"/>
+      <c r="AV204" t="inlineStr"/>
+      <c r="AW204" t="inlineStr"/>
+      <c r="AX204" t="inlineStr"/>
+      <c r="AY204" t="inlineStr"/>
+      <c r="AZ204" t="inlineStr"/>
+      <c r="BA204" t="inlineStr"/>
+      <c r="BB204" t="inlineStr"/>
+      <c r="BC204" t="inlineStr"/>
+      <c r="BD204" t="inlineStr"/>
+      <c r="BE204" t="inlineStr"/>
+      <c r="BF204" t="inlineStr"/>
+      <c r="BG204" t="inlineStr"/>
+      <c r="BH204" t="inlineStr"/>
+      <c r="BI204" t="inlineStr"/>
+      <c r="BJ204" t="inlineStr"/>
+      <c r="BK204" t="inlineStr"/>
+      <c r="BL204" t="inlineStr"/>
+      <c r="BM204" t="inlineStr"/>
+      <c r="BN204" t="inlineStr"/>
+      <c r="BO204" t="inlineStr"/>
+      <c r="BP204" t="inlineStr"/>
+      <c r="BQ204" t="inlineStr"/>
+      <c r="BR204" t="inlineStr"/>
+      <c r="BS204" t="inlineStr"/>
+      <c r="BT204" t="inlineStr"/>
+      <c r="BU204" t="inlineStr"/>
+      <c r="BV204" t="inlineStr"/>
+      <c r="BW204" t="inlineStr"/>
+      <c r="BX204" t="inlineStr"/>
+      <c r="BY204" t="inlineStr"/>
+      <c r="BZ204" t="inlineStr"/>
+      <c r="CA204" t="inlineStr"/>
+      <c r="CB204" t="inlineStr"/>
+      <c r="CC204" t="inlineStr"/>
+      <c r="CD204" t="inlineStr"/>
+      <c r="CE204" t="inlineStr"/>
+      <c r="CF204" t="inlineStr"/>
+      <c r="CG204" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gafor_log.xlsx
+++ b/data/gafor_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CG204"/>
+  <dimension ref="A1:CG205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27436,6 +27436,137 @@
       <c r="CF204" t="inlineStr"/>
       <c r="CG204" t="inlineStr"/>
     </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2026-10-18 08:00</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Ostfriesland</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Nordfriesland-Dithmarschen</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Schleswig-Holsteinische Geest</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>Schleswig-Holsteinisches Hügelland</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>Nordwestliches Niedersachsen</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>Lüneburger Heide</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Westliches Niedersachsen</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>Hannover und Braunschweig</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>Teutoburger Wald</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Weser-Leine-Bergland</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr"/>
+      <c r="M205" t="inlineStr"/>
+      <c r="N205" t="inlineStr"/>
+      <c r="O205" t="inlineStr"/>
+      <c r="P205" t="inlineStr"/>
+      <c r="Q205" t="inlineStr"/>
+      <c r="R205" t="inlineStr"/>
+      <c r="S205" t="inlineStr"/>
+      <c r="T205" t="inlineStr"/>
+      <c r="U205" t="inlineStr"/>
+      <c r="V205" t="inlineStr"/>
+      <c r="W205" t="inlineStr"/>
+      <c r="X205" t="inlineStr"/>
+      <c r="Y205" t="inlineStr"/>
+      <c r="Z205" t="inlineStr"/>
+      <c r="AA205" t="inlineStr"/>
+      <c r="AB205" t="inlineStr"/>
+      <c r="AC205" t="inlineStr"/>
+      <c r="AD205" t="inlineStr"/>
+      <c r="AE205" t="inlineStr"/>
+      <c r="AF205" t="inlineStr"/>
+      <c r="AG205" t="inlineStr"/>
+      <c r="AH205" t="inlineStr"/>
+      <c r="AI205" t="inlineStr"/>
+      <c r="AJ205" t="inlineStr"/>
+      <c r="AK205" t="inlineStr"/>
+      <c r="AL205" t="inlineStr"/>
+      <c r="AM205" t="inlineStr"/>
+      <c r="AN205" t="inlineStr"/>
+      <c r="AO205" t="inlineStr"/>
+      <c r="AP205" t="inlineStr"/>
+      <c r="AQ205" t="inlineStr"/>
+      <c r="AR205" t="inlineStr"/>
+      <c r="AS205" t="inlineStr"/>
+      <c r="AT205" t="inlineStr"/>
+      <c r="AU205" t="inlineStr"/>
+      <c r="AV205" t="inlineStr"/>
+      <c r="AW205" t="inlineStr"/>
+      <c r="AX205" t="inlineStr"/>
+      <c r="AY205" t="inlineStr"/>
+      <c r="AZ205" t="inlineStr"/>
+      <c r="BA205" t="inlineStr"/>
+      <c r="BB205" t="inlineStr"/>
+      <c r="BC205" t="inlineStr"/>
+      <c r="BD205" t="inlineStr"/>
+      <c r="BE205" t="inlineStr"/>
+      <c r="BF205" t="inlineStr"/>
+      <c r="BG205" t="inlineStr"/>
+      <c r="BH205" t="inlineStr"/>
+      <c r="BI205" t="inlineStr"/>
+      <c r="BJ205" t="inlineStr"/>
+      <c r="BK205" t="inlineStr"/>
+      <c r="BL205" t="inlineStr"/>
+      <c r="BM205" t="inlineStr"/>
+      <c r="BN205" t="inlineStr"/>
+      <c r="BO205" t="inlineStr"/>
+      <c r="BP205" t="inlineStr"/>
+      <c r="BQ205" t="inlineStr"/>
+      <c r="BR205" t="inlineStr"/>
+      <c r="BS205" t="inlineStr"/>
+      <c r="BT205" t="inlineStr"/>
+      <c r="BU205" t="inlineStr"/>
+      <c r="BV205" t="inlineStr"/>
+      <c r="BW205" t="inlineStr"/>
+      <c r="BX205" t="inlineStr"/>
+      <c r="BY205" t="inlineStr"/>
+      <c r="BZ205" t="inlineStr"/>
+      <c r="CA205" t="inlineStr"/>
+      <c r="CB205" t="inlineStr"/>
+      <c r="CC205" t="inlineStr"/>
+      <c r="CD205" t="inlineStr"/>
+      <c r="CE205" t="inlineStr"/>
+      <c r="CF205" t="inlineStr"/>
+      <c r="CG205" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gafor_log.xlsx
+++ b/data/gafor_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CG205"/>
+  <dimension ref="A1:CG206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27567,6 +27567,137 @@
       <c r="CF205" t="inlineStr"/>
       <c r="CG205" t="inlineStr"/>
     </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2026-10-19 08:00</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Ostfriesland</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Nordfriesland-Dithmarschen</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Schleswig-Holsteinische Geest</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>Schleswig-Holsteinisches Hügelland</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>Nordwestliches Niedersachsen</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>Lüneburger Heide</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Westliches Niedersachsen</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>Hannover und Braunschweig</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>Teutoburger Wald</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Weser-Leine-Bergland</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr"/>
+      <c r="M206" t="inlineStr"/>
+      <c r="N206" t="inlineStr"/>
+      <c r="O206" t="inlineStr"/>
+      <c r="P206" t="inlineStr"/>
+      <c r="Q206" t="inlineStr"/>
+      <c r="R206" t="inlineStr"/>
+      <c r="S206" t="inlineStr"/>
+      <c r="T206" t="inlineStr"/>
+      <c r="U206" t="inlineStr"/>
+      <c r="V206" t="inlineStr"/>
+      <c r="W206" t="inlineStr"/>
+      <c r="X206" t="inlineStr"/>
+      <c r="Y206" t="inlineStr"/>
+      <c r="Z206" t="inlineStr"/>
+      <c r="AA206" t="inlineStr"/>
+      <c r="AB206" t="inlineStr"/>
+      <c r="AC206" t="inlineStr"/>
+      <c r="AD206" t="inlineStr"/>
+      <c r="AE206" t="inlineStr"/>
+      <c r="AF206" t="inlineStr"/>
+      <c r="AG206" t="inlineStr"/>
+      <c r="AH206" t="inlineStr"/>
+      <c r="AI206" t="inlineStr"/>
+      <c r="AJ206" t="inlineStr"/>
+      <c r="AK206" t="inlineStr"/>
+      <c r="AL206" t="inlineStr"/>
+      <c r="AM206" t="inlineStr"/>
+      <c r="AN206" t="inlineStr"/>
+      <c r="AO206" t="inlineStr"/>
+      <c r="AP206" t="inlineStr"/>
+      <c r="AQ206" t="inlineStr"/>
+      <c r="AR206" t="inlineStr"/>
+      <c r="AS206" t="inlineStr"/>
+      <c r="AT206" t="inlineStr"/>
+      <c r="AU206" t="inlineStr"/>
+      <c r="AV206" t="inlineStr"/>
+      <c r="AW206" t="inlineStr"/>
+      <c r="AX206" t="inlineStr"/>
+      <c r="AY206" t="inlineStr"/>
+      <c r="AZ206" t="inlineStr"/>
+      <c r="BA206" t="inlineStr"/>
+      <c r="BB206" t="inlineStr"/>
+      <c r="BC206" t="inlineStr"/>
+      <c r="BD206" t="inlineStr"/>
+      <c r="BE206" t="inlineStr"/>
+      <c r="BF206" t="inlineStr"/>
+      <c r="BG206" t="inlineStr"/>
+      <c r="BH206" t="inlineStr"/>
+      <c r="BI206" t="inlineStr"/>
+      <c r="BJ206" t="inlineStr"/>
+      <c r="BK206" t="inlineStr"/>
+      <c r="BL206" t="inlineStr"/>
+      <c r="BM206" t="inlineStr"/>
+      <c r="BN206" t="inlineStr"/>
+      <c r="BO206" t="inlineStr"/>
+      <c r="BP206" t="inlineStr"/>
+      <c r="BQ206" t="inlineStr"/>
+      <c r="BR206" t="inlineStr"/>
+      <c r="BS206" t="inlineStr"/>
+      <c r="BT206" t="inlineStr"/>
+      <c r="BU206" t="inlineStr"/>
+      <c r="BV206" t="inlineStr"/>
+      <c r="BW206" t="inlineStr"/>
+      <c r="BX206" t="inlineStr"/>
+      <c r="BY206" t="inlineStr"/>
+      <c r="BZ206" t="inlineStr"/>
+      <c r="CA206" t="inlineStr"/>
+      <c r="CB206" t="inlineStr"/>
+      <c r="CC206" t="inlineStr"/>
+      <c r="CD206" t="inlineStr"/>
+      <c r="CE206" t="inlineStr"/>
+      <c r="CF206" t="inlineStr"/>
+      <c r="CG206" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gafor_log.xlsx
+++ b/data/gafor_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CG206"/>
+  <dimension ref="A1:CG207"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27698,6 +27698,137 @@
       <c r="CF206" t="inlineStr"/>
       <c r="CG206" t="inlineStr"/>
     </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2026-10-20 08:00</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Ostfriesland</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Nordfriesland-Dithmarschen</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Schleswig-Holsteinische Geest</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>Schleswig-Holsteinisches Hügelland</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>Nordwestliches Niedersachsen</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>Lüneburger Heide</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Westliches Niedersachsen</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>Hannover und Braunschweig</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>Teutoburger Wald</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Weser-Leine-Bergland</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr"/>
+      <c r="M207" t="inlineStr"/>
+      <c r="N207" t="inlineStr"/>
+      <c r="O207" t="inlineStr"/>
+      <c r="P207" t="inlineStr"/>
+      <c r="Q207" t="inlineStr"/>
+      <c r="R207" t="inlineStr"/>
+      <c r="S207" t="inlineStr"/>
+      <c r="T207" t="inlineStr"/>
+      <c r="U207" t="inlineStr"/>
+      <c r="V207" t="inlineStr"/>
+      <c r="W207" t="inlineStr"/>
+      <c r="X207" t="inlineStr"/>
+      <c r="Y207" t="inlineStr"/>
+      <c r="Z207" t="inlineStr"/>
+      <c r="AA207" t="inlineStr"/>
+      <c r="AB207" t="inlineStr"/>
+      <c r="AC207" t="inlineStr"/>
+      <c r="AD207" t="inlineStr"/>
+      <c r="AE207" t="inlineStr"/>
+      <c r="AF207" t="inlineStr"/>
+      <c r="AG207" t="inlineStr"/>
+      <c r="AH207" t="inlineStr"/>
+      <c r="AI207" t="inlineStr"/>
+      <c r="AJ207" t="inlineStr"/>
+      <c r="AK207" t="inlineStr"/>
+      <c r="AL207" t="inlineStr"/>
+      <c r="AM207" t="inlineStr"/>
+      <c r="AN207" t="inlineStr"/>
+      <c r="AO207" t="inlineStr"/>
+      <c r="AP207" t="inlineStr"/>
+      <c r="AQ207" t="inlineStr"/>
+      <c r="AR207" t="inlineStr"/>
+      <c r="AS207" t="inlineStr"/>
+      <c r="AT207" t="inlineStr"/>
+      <c r="AU207" t="inlineStr"/>
+      <c r="AV207" t="inlineStr"/>
+      <c r="AW207" t="inlineStr"/>
+      <c r="AX207" t="inlineStr"/>
+      <c r="AY207" t="inlineStr"/>
+      <c r="AZ207" t="inlineStr"/>
+      <c r="BA207" t="inlineStr"/>
+      <c r="BB207" t="inlineStr"/>
+      <c r="BC207" t="inlineStr"/>
+      <c r="BD207" t="inlineStr"/>
+      <c r="BE207" t="inlineStr"/>
+      <c r="BF207" t="inlineStr"/>
+      <c r="BG207" t="inlineStr"/>
+      <c r="BH207" t="inlineStr"/>
+      <c r="BI207" t="inlineStr"/>
+      <c r="BJ207" t="inlineStr"/>
+      <c r="BK207" t="inlineStr"/>
+      <c r="BL207" t="inlineStr"/>
+      <c r="BM207" t="inlineStr"/>
+      <c r="BN207" t="inlineStr"/>
+      <c r="BO207" t="inlineStr"/>
+      <c r="BP207" t="inlineStr"/>
+      <c r="BQ207" t="inlineStr"/>
+      <c r="BR207" t="inlineStr"/>
+      <c r="BS207" t="inlineStr"/>
+      <c r="BT207" t="inlineStr"/>
+      <c r="BU207" t="inlineStr"/>
+      <c r="BV207" t="inlineStr"/>
+      <c r="BW207" t="inlineStr"/>
+      <c r="BX207" t="inlineStr"/>
+      <c r="BY207" t="inlineStr"/>
+      <c r="BZ207" t="inlineStr"/>
+      <c r="CA207" t="inlineStr"/>
+      <c r="CB207" t="inlineStr"/>
+      <c r="CC207" t="inlineStr"/>
+      <c r="CD207" t="inlineStr"/>
+      <c r="CE207" t="inlineStr"/>
+      <c r="CF207" t="inlineStr"/>
+      <c r="CG207" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gafor_log.xlsx
+++ b/data/gafor_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CG207"/>
+  <dimension ref="A1:CG208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27829,6 +27829,137 @@
       <c r="CF207" t="inlineStr"/>
       <c r="CG207" t="inlineStr"/>
     </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2026-10-21 08:00</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Ostfriesland</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Nordfriesland-Dithmarschen</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Schleswig-Holsteinische Geest</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>Schleswig-Holsteinisches Hügelland</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>Nordwestliches Niedersachsen</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>Lüneburger Heide</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Westliches Niedersachsen</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>Hannover und Braunschweig</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>Teutoburger Wald</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Weser-Leine-Bergland</t>
+        </is>
+      </c>
+      <c r="L208" t="inlineStr"/>
+      <c r="M208" t="inlineStr"/>
+      <c r="N208" t="inlineStr"/>
+      <c r="O208" t="inlineStr"/>
+      <c r="P208" t="inlineStr"/>
+      <c r="Q208" t="inlineStr"/>
+      <c r="R208" t="inlineStr"/>
+      <c r="S208" t="inlineStr"/>
+      <c r="T208" t="inlineStr"/>
+      <c r="U208" t="inlineStr"/>
+      <c r="V208" t="inlineStr"/>
+      <c r="W208" t="inlineStr"/>
+      <c r="X208" t="inlineStr"/>
+      <c r="Y208" t="inlineStr"/>
+      <c r="Z208" t="inlineStr"/>
+      <c r="AA208" t="inlineStr"/>
+      <c r="AB208" t="inlineStr"/>
+      <c r="AC208" t="inlineStr"/>
+      <c r="AD208" t="inlineStr"/>
+      <c r="AE208" t="inlineStr"/>
+      <c r="AF208" t="inlineStr"/>
+      <c r="AG208" t="inlineStr"/>
+      <c r="AH208" t="inlineStr"/>
+      <c r="AI208" t="inlineStr"/>
+      <c r="AJ208" t="inlineStr"/>
+      <c r="AK208" t="inlineStr"/>
+      <c r="AL208" t="inlineStr"/>
+      <c r="AM208" t="inlineStr"/>
+      <c r="AN208" t="inlineStr"/>
+      <c r="AO208" t="inlineStr"/>
+      <c r="AP208" t="inlineStr"/>
+      <c r="AQ208" t="inlineStr"/>
+      <c r="AR208" t="inlineStr"/>
+      <c r="AS208" t="inlineStr"/>
+      <c r="AT208" t="inlineStr"/>
+      <c r="AU208" t="inlineStr"/>
+      <c r="AV208" t="inlineStr"/>
+      <c r="AW208" t="inlineStr"/>
+      <c r="AX208" t="inlineStr"/>
+      <c r="AY208" t="inlineStr"/>
+      <c r="AZ208" t="inlineStr"/>
+      <c r="BA208" t="inlineStr"/>
+      <c r="BB208" t="inlineStr"/>
+      <c r="BC208" t="inlineStr"/>
+      <c r="BD208" t="inlineStr"/>
+      <c r="BE208" t="inlineStr"/>
+      <c r="BF208" t="inlineStr"/>
+      <c r="BG208" t="inlineStr"/>
+      <c r="BH208" t="inlineStr"/>
+      <c r="BI208" t="inlineStr"/>
+      <c r="BJ208" t="inlineStr"/>
+      <c r="BK208" t="inlineStr"/>
+      <c r="BL208" t="inlineStr"/>
+      <c r="BM208" t="inlineStr"/>
+      <c r="BN208" t="inlineStr"/>
+      <c r="BO208" t="inlineStr"/>
+      <c r="BP208" t="inlineStr"/>
+      <c r="BQ208" t="inlineStr"/>
+      <c r="BR208" t="inlineStr"/>
+      <c r="BS208" t="inlineStr"/>
+      <c r="BT208" t="inlineStr"/>
+      <c r="BU208" t="inlineStr"/>
+      <c r="BV208" t="inlineStr"/>
+      <c r="BW208" t="inlineStr"/>
+      <c r="BX208" t="inlineStr"/>
+      <c r="BY208" t="inlineStr"/>
+      <c r="BZ208" t="inlineStr"/>
+      <c r="CA208" t="inlineStr"/>
+      <c r="CB208" t="inlineStr"/>
+      <c r="CC208" t="inlineStr"/>
+      <c r="CD208" t="inlineStr"/>
+      <c r="CE208" t="inlineStr"/>
+      <c r="CF208" t="inlineStr"/>
+      <c r="CG208" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gafor_log.xlsx
+++ b/data/gafor_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CG208"/>
+  <dimension ref="A1:CG209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27960,6 +27960,137 @@
       <c r="CF208" t="inlineStr"/>
       <c r="CG208" t="inlineStr"/>
     </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2026-10-22 08:00</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Ostfriesland</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Nordfriesland-Dithmarschen</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Schleswig-Holsteinische Geest</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>Schleswig-Holsteinisches Hügelland</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>Nordwestliches Niedersachsen</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>Lüneburger Heide</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Westliches Niedersachsen</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>Hannover und Braunschweig</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>Teutoburger Wald</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Weser-Leine-Bergland</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr"/>
+      <c r="M209" t="inlineStr"/>
+      <c r="N209" t="inlineStr"/>
+      <c r="O209" t="inlineStr"/>
+      <c r="P209" t="inlineStr"/>
+      <c r="Q209" t="inlineStr"/>
+      <c r="R209" t="inlineStr"/>
+      <c r="S209" t="inlineStr"/>
+      <c r="T209" t="inlineStr"/>
+      <c r="U209" t="inlineStr"/>
+      <c r="V209" t="inlineStr"/>
+      <c r="W209" t="inlineStr"/>
+      <c r="X209" t="inlineStr"/>
+      <c r="Y209" t="inlineStr"/>
+      <c r="Z209" t="inlineStr"/>
+      <c r="AA209" t="inlineStr"/>
+      <c r="AB209" t="inlineStr"/>
+      <c r="AC209" t="inlineStr"/>
+      <c r="AD209" t="inlineStr"/>
+      <c r="AE209" t="inlineStr"/>
+      <c r="AF209" t="inlineStr"/>
+      <c r="AG209" t="inlineStr"/>
+      <c r="AH209" t="inlineStr"/>
+      <c r="AI209" t="inlineStr"/>
+      <c r="AJ209" t="inlineStr"/>
+      <c r="AK209" t="inlineStr"/>
+      <c r="AL209" t="inlineStr"/>
+      <c r="AM209" t="inlineStr"/>
+      <c r="AN209" t="inlineStr"/>
+      <c r="AO209" t="inlineStr"/>
+      <c r="AP209" t="inlineStr"/>
+      <c r="AQ209" t="inlineStr"/>
+      <c r="AR209" t="inlineStr"/>
+      <c r="AS209" t="inlineStr"/>
+      <c r="AT209" t="inlineStr"/>
+      <c r="AU209" t="inlineStr"/>
+      <c r="AV209" t="inlineStr"/>
+      <c r="AW209" t="inlineStr"/>
+      <c r="AX209" t="inlineStr"/>
+      <c r="AY209" t="inlineStr"/>
+      <c r="AZ209" t="inlineStr"/>
+      <c r="BA209" t="inlineStr"/>
+      <c r="BB209" t="inlineStr"/>
+      <c r="BC209" t="inlineStr"/>
+      <c r="BD209" t="inlineStr"/>
+      <c r="BE209" t="inlineStr"/>
+      <c r="BF209" t="inlineStr"/>
+      <c r="BG209" t="inlineStr"/>
+      <c r="BH209" t="inlineStr"/>
+      <c r="BI209" t="inlineStr"/>
+      <c r="BJ209" t="inlineStr"/>
+      <c r="BK209" t="inlineStr"/>
+      <c r="BL209" t="inlineStr"/>
+      <c r="BM209" t="inlineStr"/>
+      <c r="BN209" t="inlineStr"/>
+      <c r="BO209" t="inlineStr"/>
+      <c r="BP209" t="inlineStr"/>
+      <c r="BQ209" t="inlineStr"/>
+      <c r="BR209" t="inlineStr"/>
+      <c r="BS209" t="inlineStr"/>
+      <c r="BT209" t="inlineStr"/>
+      <c r="BU209" t="inlineStr"/>
+      <c r="BV209" t="inlineStr"/>
+      <c r="BW209" t="inlineStr"/>
+      <c r="BX209" t="inlineStr"/>
+      <c r="BY209" t="inlineStr"/>
+      <c r="BZ209" t="inlineStr"/>
+      <c r="CA209" t="inlineStr"/>
+      <c r="CB209" t="inlineStr"/>
+      <c r="CC209" t="inlineStr"/>
+      <c r="CD209" t="inlineStr"/>
+      <c r="CE209" t="inlineStr"/>
+      <c r="CF209" t="inlineStr"/>
+      <c r="CG209" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gafor_log.xlsx
+++ b/data/gafor_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CG209"/>
+  <dimension ref="A1:CG210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28091,6 +28091,137 @@
       <c r="CF209" t="inlineStr"/>
       <c r="CG209" t="inlineStr"/>
     </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2026-10-23 08:00</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Ostfriesland</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Nordfriesland-Dithmarschen</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Schleswig-Holsteinische Geest</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>Schleswig-Holsteinisches Hügelland</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>Nordwestliches Niedersachsen</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>Lüneburger Heide</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>Westliches Niedersachsen</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>Hannover und Braunschweig</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>Teutoburger Wald</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Weser-Leine-Bergland</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr"/>
+      <c r="M210" t="inlineStr"/>
+      <c r="N210" t="inlineStr"/>
+      <c r="O210" t="inlineStr"/>
+      <c r="P210" t="inlineStr"/>
+      <c r="Q210" t="inlineStr"/>
+      <c r="R210" t="inlineStr"/>
+      <c r="S210" t="inlineStr"/>
+      <c r="T210" t="inlineStr"/>
+      <c r="U210" t="inlineStr"/>
+      <c r="V210" t="inlineStr"/>
+      <c r="W210" t="inlineStr"/>
+      <c r="X210" t="inlineStr"/>
+      <c r="Y210" t="inlineStr"/>
+      <c r="Z210" t="inlineStr"/>
+      <c r="AA210" t="inlineStr"/>
+      <c r="AB210" t="inlineStr"/>
+      <c r="AC210" t="inlineStr"/>
+      <c r="AD210" t="inlineStr"/>
+      <c r="AE210" t="inlineStr"/>
+      <c r="AF210" t="inlineStr"/>
+      <c r="AG210" t="inlineStr"/>
+      <c r="AH210" t="inlineStr"/>
+      <c r="AI210" t="inlineStr"/>
+      <c r="AJ210" t="inlineStr"/>
+      <c r="AK210" t="inlineStr"/>
+      <c r="AL210" t="inlineStr"/>
+      <c r="AM210" t="inlineStr"/>
+      <c r="AN210" t="inlineStr"/>
+      <c r="AO210" t="inlineStr"/>
+      <c r="AP210" t="inlineStr"/>
+      <c r="AQ210" t="inlineStr"/>
+      <c r="AR210" t="inlineStr"/>
+      <c r="AS210" t="inlineStr"/>
+      <c r="AT210" t="inlineStr"/>
+      <c r="AU210" t="inlineStr"/>
+      <c r="AV210" t="inlineStr"/>
+      <c r="AW210" t="inlineStr"/>
+      <c r="AX210" t="inlineStr"/>
+      <c r="AY210" t="inlineStr"/>
+      <c r="AZ210" t="inlineStr"/>
+      <c r="BA210" t="inlineStr"/>
+      <c r="BB210" t="inlineStr"/>
+      <c r="BC210" t="inlineStr"/>
+      <c r="BD210" t="inlineStr"/>
+      <c r="BE210" t="inlineStr"/>
+      <c r="BF210" t="inlineStr"/>
+      <c r="BG210" t="inlineStr"/>
+      <c r="BH210" t="inlineStr"/>
+      <c r="BI210" t="inlineStr"/>
+      <c r="BJ210" t="inlineStr"/>
+      <c r="BK210" t="inlineStr"/>
+      <c r="BL210" t="inlineStr"/>
+      <c r="BM210" t="inlineStr"/>
+      <c r="BN210" t="inlineStr"/>
+      <c r="BO210" t="inlineStr"/>
+      <c r="BP210" t="inlineStr"/>
+      <c r="BQ210" t="inlineStr"/>
+      <c r="BR210" t="inlineStr"/>
+      <c r="BS210" t="inlineStr"/>
+      <c r="BT210" t="inlineStr"/>
+      <c r="BU210" t="inlineStr"/>
+      <c r="BV210" t="inlineStr"/>
+      <c r="BW210" t="inlineStr"/>
+      <c r="BX210" t="inlineStr"/>
+      <c r="BY210" t="inlineStr"/>
+      <c r="BZ210" t="inlineStr"/>
+      <c r="CA210" t="inlineStr"/>
+      <c r="CB210" t="inlineStr"/>
+      <c r="CC210" t="inlineStr"/>
+      <c r="CD210" t="inlineStr"/>
+      <c r="CE210" t="inlineStr"/>
+      <c r="CF210" t="inlineStr"/>
+      <c r="CG210" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gafor_log.xlsx
+++ b/data/gafor_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CG210"/>
+  <dimension ref="A1:CG211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28222,6 +28222,137 @@
       <c r="CF210" t="inlineStr"/>
       <c r="CG210" t="inlineStr"/>
     </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2026-10-24 08:00</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Ostfriesland</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Nordfriesland-Dithmarschen</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Schleswig-Holsteinische Geest</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Schleswig-Holsteinisches Hügelland</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>Nordwestliches Niedersachsen</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>Lüneburger Heide</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Westliches Niedersachsen</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>Hannover und Braunschweig</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>Teutoburger Wald</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Weser-Leine-Bergland</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr"/>
+      <c r="M211" t="inlineStr"/>
+      <c r="N211" t="inlineStr"/>
+      <c r="O211" t="inlineStr"/>
+      <c r="P211" t="inlineStr"/>
+      <c r="Q211" t="inlineStr"/>
+      <c r="R211" t="inlineStr"/>
+      <c r="S211" t="inlineStr"/>
+      <c r="T211" t="inlineStr"/>
+      <c r="U211" t="inlineStr"/>
+      <c r="V211" t="inlineStr"/>
+      <c r="W211" t="inlineStr"/>
+      <c r="X211" t="inlineStr"/>
+      <c r="Y211" t="inlineStr"/>
+      <c r="Z211" t="inlineStr"/>
+      <c r="AA211" t="inlineStr"/>
+      <c r="AB211" t="inlineStr"/>
+      <c r="AC211" t="inlineStr"/>
+      <c r="AD211" t="inlineStr"/>
+      <c r="AE211" t="inlineStr"/>
+      <c r="AF211" t="inlineStr"/>
+      <c r="AG211" t="inlineStr"/>
+      <c r="AH211" t="inlineStr"/>
+      <c r="AI211" t="inlineStr"/>
+      <c r="AJ211" t="inlineStr"/>
+      <c r="AK211" t="inlineStr"/>
+      <c r="AL211" t="inlineStr"/>
+      <c r="AM211" t="inlineStr"/>
+      <c r="AN211" t="inlineStr"/>
+      <c r="AO211" t="inlineStr"/>
+      <c r="AP211" t="inlineStr"/>
+      <c r="AQ211" t="inlineStr"/>
+      <c r="AR211" t="inlineStr"/>
+      <c r="AS211" t="inlineStr"/>
+      <c r="AT211" t="inlineStr"/>
+      <c r="AU211" t="inlineStr"/>
+      <c r="AV211" t="inlineStr"/>
+      <c r="AW211" t="inlineStr"/>
+      <c r="AX211" t="inlineStr"/>
+      <c r="AY211" t="inlineStr"/>
+      <c r="AZ211" t="inlineStr"/>
+      <c r="BA211" t="inlineStr"/>
+      <c r="BB211" t="inlineStr"/>
+      <c r="BC211" t="inlineStr"/>
+      <c r="BD211" t="inlineStr"/>
+      <c r="BE211" t="inlineStr"/>
+      <c r="BF211" t="inlineStr"/>
+      <c r="BG211" t="inlineStr"/>
+      <c r="BH211" t="inlineStr"/>
+      <c r="BI211" t="inlineStr"/>
+      <c r="BJ211" t="inlineStr"/>
+      <c r="BK211" t="inlineStr"/>
+      <c r="BL211" t="inlineStr"/>
+      <c r="BM211" t="inlineStr"/>
+      <c r="BN211" t="inlineStr"/>
+      <c r="BO211" t="inlineStr"/>
+      <c r="BP211" t="inlineStr"/>
+      <c r="BQ211" t="inlineStr"/>
+      <c r="BR211" t="inlineStr"/>
+      <c r="BS211" t="inlineStr"/>
+      <c r="BT211" t="inlineStr"/>
+      <c r="BU211" t="inlineStr"/>
+      <c r="BV211" t="inlineStr"/>
+      <c r="BW211" t="inlineStr"/>
+      <c r="BX211" t="inlineStr"/>
+      <c r="BY211" t="inlineStr"/>
+      <c r="BZ211" t="inlineStr"/>
+      <c r="CA211" t="inlineStr"/>
+      <c r="CB211" t="inlineStr"/>
+      <c r="CC211" t="inlineStr"/>
+      <c r="CD211" t="inlineStr"/>
+      <c r="CE211" t="inlineStr"/>
+      <c r="CF211" t="inlineStr"/>
+      <c r="CG211" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gafor_log.xlsx
+++ b/data/gafor_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CG211"/>
+  <dimension ref="A1:CG212"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28353,6 +28353,137 @@
       <c r="CF211" t="inlineStr"/>
       <c r="CG211" t="inlineStr"/>
     </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2026-10-25 08:00</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Ostfriesland</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Nordfriesland-Dithmarschen</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Schleswig-Holsteinische Geest</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>Schleswig-Holsteinisches Hügelland</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>Nordwestliches Niedersachsen</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>Lüneburger Heide</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>Westliches Niedersachsen</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>Hannover und Braunschweig</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>Teutoburger Wald</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Weser-Leine-Bergland</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr"/>
+      <c r="M212" t="inlineStr"/>
+      <c r="N212" t="inlineStr"/>
+      <c r="O212" t="inlineStr"/>
+      <c r="P212" t="inlineStr"/>
+      <c r="Q212" t="inlineStr"/>
+      <c r="R212" t="inlineStr"/>
+      <c r="S212" t="inlineStr"/>
+      <c r="T212" t="inlineStr"/>
+      <c r="U212" t="inlineStr"/>
+      <c r="V212" t="inlineStr"/>
+      <c r="W212" t="inlineStr"/>
+      <c r="X212" t="inlineStr"/>
+      <c r="Y212" t="inlineStr"/>
+      <c r="Z212" t="inlineStr"/>
+      <c r="AA212" t="inlineStr"/>
+      <c r="AB212" t="inlineStr"/>
+      <c r="AC212" t="inlineStr"/>
+      <c r="AD212" t="inlineStr"/>
+      <c r="AE212" t="inlineStr"/>
+      <c r="AF212" t="inlineStr"/>
+      <c r="AG212" t="inlineStr"/>
+      <c r="AH212" t="inlineStr"/>
+      <c r="AI212" t="inlineStr"/>
+      <c r="AJ212" t="inlineStr"/>
+      <c r="AK212" t="inlineStr"/>
+      <c r="AL212" t="inlineStr"/>
+      <c r="AM212" t="inlineStr"/>
+      <c r="AN212" t="inlineStr"/>
+      <c r="AO212" t="inlineStr"/>
+      <c r="AP212" t="inlineStr"/>
+      <c r="AQ212" t="inlineStr"/>
+      <c r="AR212" t="inlineStr"/>
+      <c r="AS212" t="inlineStr"/>
+      <c r="AT212" t="inlineStr"/>
+      <c r="AU212" t="inlineStr"/>
+      <c r="AV212" t="inlineStr"/>
+      <c r="AW212" t="inlineStr"/>
+      <c r="AX212" t="inlineStr"/>
+      <c r="AY212" t="inlineStr"/>
+      <c r="AZ212" t="inlineStr"/>
+      <c r="BA212" t="inlineStr"/>
+      <c r="BB212" t="inlineStr"/>
+      <c r="BC212" t="inlineStr"/>
+      <c r="BD212" t="inlineStr"/>
+      <c r="BE212" t="inlineStr"/>
+      <c r="BF212" t="inlineStr"/>
+      <c r="BG212" t="inlineStr"/>
+      <c r="BH212" t="inlineStr"/>
+      <c r="BI212" t="inlineStr"/>
+      <c r="BJ212" t="inlineStr"/>
+      <c r="BK212" t="inlineStr"/>
+      <c r="BL212" t="inlineStr"/>
+      <c r="BM212" t="inlineStr"/>
+      <c r="BN212" t="inlineStr"/>
+      <c r="BO212" t="inlineStr"/>
+      <c r="BP212" t="inlineStr"/>
+      <c r="BQ212" t="inlineStr"/>
+      <c r="BR212" t="inlineStr"/>
+      <c r="BS212" t="inlineStr"/>
+      <c r="BT212" t="inlineStr"/>
+      <c r="BU212" t="inlineStr"/>
+      <c r="BV212" t="inlineStr"/>
+      <c r="BW212" t="inlineStr"/>
+      <c r="BX212" t="inlineStr"/>
+      <c r="BY212" t="inlineStr"/>
+      <c r="BZ212" t="inlineStr"/>
+      <c r="CA212" t="inlineStr"/>
+      <c r="CB212" t="inlineStr"/>
+      <c r="CC212" t="inlineStr"/>
+      <c r="CD212" t="inlineStr"/>
+      <c r="CE212" t="inlineStr"/>
+      <c r="CF212" t="inlineStr"/>
+      <c r="CG212" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gafor_log.xlsx
+++ b/data/gafor_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CG212"/>
+  <dimension ref="A1:CG213"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28484,6 +28484,137 @@
       <c r="CF212" t="inlineStr"/>
       <c r="CG212" t="inlineStr"/>
     </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2026-10-26 08:00</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Ostfriesland</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Nordfriesland-Dithmarschen</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Schleswig-Holsteinische Geest</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>Schleswig-Holsteinisches Hügelland</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>Nordwestliches Niedersachsen</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>Lüneburger Heide</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>Westliches Niedersachsen</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>Hannover und Braunschweig</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>Teutoburger Wald</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Weser-Leine-Bergland</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr"/>
+      <c r="M213" t="inlineStr"/>
+      <c r="N213" t="inlineStr"/>
+      <c r="O213" t="inlineStr"/>
+      <c r="P213" t="inlineStr"/>
+      <c r="Q213" t="inlineStr"/>
+      <c r="R213" t="inlineStr"/>
+      <c r="S213" t="inlineStr"/>
+      <c r="T213" t="inlineStr"/>
+      <c r="U213" t="inlineStr"/>
+      <c r="V213" t="inlineStr"/>
+      <c r="W213" t="inlineStr"/>
+      <c r="X213" t="inlineStr"/>
+      <c r="Y213" t="inlineStr"/>
+      <c r="Z213" t="inlineStr"/>
+      <c r="AA213" t="inlineStr"/>
+      <c r="AB213" t="inlineStr"/>
+      <c r="AC213" t="inlineStr"/>
+      <c r="AD213" t="inlineStr"/>
+      <c r="AE213" t="inlineStr"/>
+      <c r="AF213" t="inlineStr"/>
+      <c r="AG213" t="inlineStr"/>
+      <c r="AH213" t="inlineStr"/>
+      <c r="AI213" t="inlineStr"/>
+      <c r="AJ213" t="inlineStr"/>
+      <c r="AK213" t="inlineStr"/>
+      <c r="AL213" t="inlineStr"/>
+      <c r="AM213" t="inlineStr"/>
+      <c r="AN213" t="inlineStr"/>
+      <c r="AO213" t="inlineStr"/>
+      <c r="AP213" t="inlineStr"/>
+      <c r="AQ213" t="inlineStr"/>
+      <c r="AR213" t="inlineStr"/>
+      <c r="AS213" t="inlineStr"/>
+      <c r="AT213" t="inlineStr"/>
+      <c r="AU213" t="inlineStr"/>
+      <c r="AV213" t="inlineStr"/>
+      <c r="AW213" t="inlineStr"/>
+      <c r="AX213" t="inlineStr"/>
+      <c r="AY213" t="inlineStr"/>
+      <c r="AZ213" t="inlineStr"/>
+      <c r="BA213" t="inlineStr"/>
+      <c r="BB213" t="inlineStr"/>
+      <c r="BC213" t="inlineStr"/>
+      <c r="BD213" t="inlineStr"/>
+      <c r="BE213" t="inlineStr"/>
+      <c r="BF213" t="inlineStr"/>
+      <c r="BG213" t="inlineStr"/>
+      <c r="BH213" t="inlineStr"/>
+      <c r="BI213" t="inlineStr"/>
+      <c r="BJ213" t="inlineStr"/>
+      <c r="BK213" t="inlineStr"/>
+      <c r="BL213" t="inlineStr"/>
+      <c r="BM213" t="inlineStr"/>
+      <c r="BN213" t="inlineStr"/>
+      <c r="BO213" t="inlineStr"/>
+      <c r="BP213" t="inlineStr"/>
+      <c r="BQ213" t="inlineStr"/>
+      <c r="BR213" t="inlineStr"/>
+      <c r="BS213" t="inlineStr"/>
+      <c r="BT213" t="inlineStr"/>
+      <c r="BU213" t="inlineStr"/>
+      <c r="BV213" t="inlineStr"/>
+      <c r="BW213" t="inlineStr"/>
+      <c r="BX213" t="inlineStr"/>
+      <c r="BY213" t="inlineStr"/>
+      <c r="BZ213" t="inlineStr"/>
+      <c r="CA213" t="inlineStr"/>
+      <c r="CB213" t="inlineStr"/>
+      <c r="CC213" t="inlineStr"/>
+      <c r="CD213" t="inlineStr"/>
+      <c r="CE213" t="inlineStr"/>
+      <c r="CF213" t="inlineStr"/>
+      <c r="CG213" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gafor_log.xlsx
+++ b/data/gafor_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CG213"/>
+  <dimension ref="A1:CG214"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28615,6 +28615,137 @@
       <c r="CF213" t="inlineStr"/>
       <c r="CG213" t="inlineStr"/>
     </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2026-10-27 08:00</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Ostfriesland</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Nordfriesland-Dithmarschen</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Schleswig-Holsteinische Geest</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>Schleswig-Holsteinisches Hügelland</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>Nordwestliches Niedersachsen</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>Lüneburger Heide</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>Westliches Niedersachsen</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>Hannover und Braunschweig</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>Teutoburger Wald</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Weser-Leine-Bergland</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr"/>
+      <c r="M214" t="inlineStr"/>
+      <c r="N214" t="inlineStr"/>
+      <c r="O214" t="inlineStr"/>
+      <c r="P214" t="inlineStr"/>
+      <c r="Q214" t="inlineStr"/>
+      <c r="R214" t="inlineStr"/>
+      <c r="S214" t="inlineStr"/>
+      <c r="T214" t="inlineStr"/>
+      <c r="U214" t="inlineStr"/>
+      <c r="V214" t="inlineStr"/>
+      <c r="W214" t="inlineStr"/>
+      <c r="X214" t="inlineStr"/>
+      <c r="Y214" t="inlineStr"/>
+      <c r="Z214" t="inlineStr"/>
+      <c r="AA214" t="inlineStr"/>
+      <c r="AB214" t="inlineStr"/>
+      <c r="AC214" t="inlineStr"/>
+      <c r="AD214" t="inlineStr"/>
+      <c r="AE214" t="inlineStr"/>
+      <c r="AF214" t="inlineStr"/>
+      <c r="AG214" t="inlineStr"/>
+      <c r="AH214" t="inlineStr"/>
+      <c r="AI214" t="inlineStr"/>
+      <c r="AJ214" t="inlineStr"/>
+      <c r="AK214" t="inlineStr"/>
+      <c r="AL214" t="inlineStr"/>
+      <c r="AM214" t="inlineStr"/>
+      <c r="AN214" t="inlineStr"/>
+      <c r="AO214" t="inlineStr"/>
+      <c r="AP214" t="inlineStr"/>
+      <c r="AQ214" t="inlineStr"/>
+      <c r="AR214" t="inlineStr"/>
+      <c r="AS214" t="inlineStr"/>
+      <c r="AT214" t="inlineStr"/>
+      <c r="AU214" t="inlineStr"/>
+      <c r="AV214" t="inlineStr"/>
+      <c r="AW214" t="inlineStr"/>
+      <c r="AX214" t="inlineStr"/>
+      <c r="AY214" t="inlineStr"/>
+      <c r="AZ214" t="inlineStr"/>
+      <c r="BA214" t="inlineStr"/>
+      <c r="BB214" t="inlineStr"/>
+      <c r="BC214" t="inlineStr"/>
+      <c r="BD214" t="inlineStr"/>
+      <c r="BE214" t="inlineStr"/>
+      <c r="BF214" t="inlineStr"/>
+      <c r="BG214" t="inlineStr"/>
+      <c r="BH214" t="inlineStr"/>
+      <c r="BI214" t="inlineStr"/>
+      <c r="BJ214" t="inlineStr"/>
+      <c r="BK214" t="inlineStr"/>
+      <c r="BL214" t="inlineStr"/>
+      <c r="BM214" t="inlineStr"/>
+      <c r="BN214" t="inlineStr"/>
+      <c r="BO214" t="inlineStr"/>
+      <c r="BP214" t="inlineStr"/>
+      <c r="BQ214" t="inlineStr"/>
+      <c r="BR214" t="inlineStr"/>
+      <c r="BS214" t="inlineStr"/>
+      <c r="BT214" t="inlineStr"/>
+      <c r="BU214" t="inlineStr"/>
+      <c r="BV214" t="inlineStr"/>
+      <c r="BW214" t="inlineStr"/>
+      <c r="BX214" t="inlineStr"/>
+      <c r="BY214" t="inlineStr"/>
+      <c r="BZ214" t="inlineStr"/>
+      <c r="CA214" t="inlineStr"/>
+      <c r="CB214" t="inlineStr"/>
+      <c r="CC214" t="inlineStr"/>
+      <c r="CD214" t="inlineStr"/>
+      <c r="CE214" t="inlineStr"/>
+      <c r="CF214" t="inlineStr"/>
+      <c r="CG214" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gafor_log.xlsx
+++ b/data/gafor_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CG214"/>
+  <dimension ref="A1:CG215"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28746,6 +28746,137 @@
       <c r="CF214" t="inlineStr"/>
       <c r="CG214" t="inlineStr"/>
     </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2026-10-28 08:00</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Ostfriesland</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Nordfriesland-Dithmarschen</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Schleswig-Holsteinische Geest</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>Schleswig-Holsteinisches Hügelland</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>Nordwestliches Niedersachsen</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>Lüneburger Heide</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>Westliches Niedersachsen</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>Hannover und Braunschweig</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>Teutoburger Wald</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Weser-Leine-Bergland</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr"/>
+      <c r="M215" t="inlineStr"/>
+      <c r="N215" t="inlineStr"/>
+      <c r="O215" t="inlineStr"/>
+      <c r="P215" t="inlineStr"/>
+      <c r="Q215" t="inlineStr"/>
+      <c r="R215" t="inlineStr"/>
+      <c r="S215" t="inlineStr"/>
+      <c r="T215" t="inlineStr"/>
+      <c r="U215" t="inlineStr"/>
+      <c r="V215" t="inlineStr"/>
+      <c r="W215" t="inlineStr"/>
+      <c r="X215" t="inlineStr"/>
+      <c r="Y215" t="inlineStr"/>
+      <c r="Z215" t="inlineStr"/>
+      <c r="AA215" t="inlineStr"/>
+      <c r="AB215" t="inlineStr"/>
+      <c r="AC215" t="inlineStr"/>
+      <c r="AD215" t="inlineStr"/>
+      <c r="AE215" t="inlineStr"/>
+      <c r="AF215" t="inlineStr"/>
+      <c r="AG215" t="inlineStr"/>
+      <c r="AH215" t="inlineStr"/>
+      <c r="AI215" t="inlineStr"/>
+      <c r="AJ215" t="inlineStr"/>
+      <c r="AK215" t="inlineStr"/>
+      <c r="AL215" t="inlineStr"/>
+      <c r="AM215" t="inlineStr"/>
+      <c r="AN215" t="inlineStr"/>
+      <c r="AO215" t="inlineStr"/>
+      <c r="AP215" t="inlineStr"/>
+      <c r="AQ215" t="inlineStr"/>
+      <c r="AR215" t="inlineStr"/>
+      <c r="AS215" t="inlineStr"/>
+      <c r="AT215" t="inlineStr"/>
+      <c r="AU215" t="inlineStr"/>
+      <c r="AV215" t="inlineStr"/>
+      <c r="AW215" t="inlineStr"/>
+      <c r="AX215" t="inlineStr"/>
+      <c r="AY215" t="inlineStr"/>
+      <c r="AZ215" t="inlineStr"/>
+      <c r="BA215" t="inlineStr"/>
+      <c r="BB215" t="inlineStr"/>
+      <c r="BC215" t="inlineStr"/>
+      <c r="BD215" t="inlineStr"/>
+      <c r="BE215" t="inlineStr"/>
+      <c r="BF215" t="inlineStr"/>
+      <c r="BG215" t="inlineStr"/>
+      <c r="BH215" t="inlineStr"/>
+      <c r="BI215" t="inlineStr"/>
+      <c r="BJ215" t="inlineStr"/>
+      <c r="BK215" t="inlineStr"/>
+      <c r="BL215" t="inlineStr"/>
+      <c r="BM215" t="inlineStr"/>
+      <c r="BN215" t="inlineStr"/>
+      <c r="BO215" t="inlineStr"/>
+      <c r="BP215" t="inlineStr"/>
+      <c r="BQ215" t="inlineStr"/>
+      <c r="BR215" t="inlineStr"/>
+      <c r="BS215" t="inlineStr"/>
+      <c r="BT215" t="inlineStr"/>
+      <c r="BU215" t="inlineStr"/>
+      <c r="BV215" t="inlineStr"/>
+      <c r="BW215" t="inlineStr"/>
+      <c r="BX215" t="inlineStr"/>
+      <c r="BY215" t="inlineStr"/>
+      <c r="BZ215" t="inlineStr"/>
+      <c r="CA215" t="inlineStr"/>
+      <c r="CB215" t="inlineStr"/>
+      <c r="CC215" t="inlineStr"/>
+      <c r="CD215" t="inlineStr"/>
+      <c r="CE215" t="inlineStr"/>
+      <c r="CF215" t="inlineStr"/>
+      <c r="CG215" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gafor_log.xlsx
+++ b/data/gafor_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CG215"/>
+  <dimension ref="A1:CG216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28877,6 +28877,137 @@
       <c r="CF215" t="inlineStr"/>
       <c r="CG215" t="inlineStr"/>
     </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2026-10-29 08:00</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Ostfriesland</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Nordfriesland-Dithmarschen</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Schleswig-Holsteinische Geest</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>Schleswig-Holsteinisches Hügelland</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>Nordwestliches Niedersachsen</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>Lüneburger Heide</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>Westliches Niedersachsen</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>Hannover und Braunschweig</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>Teutoburger Wald</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Weser-Leine-Bergland</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr"/>
+      <c r="M216" t="inlineStr"/>
+      <c r="N216" t="inlineStr"/>
+      <c r="O216" t="inlineStr"/>
+      <c r="P216" t="inlineStr"/>
+      <c r="Q216" t="inlineStr"/>
+      <c r="R216" t="inlineStr"/>
+      <c r="S216" t="inlineStr"/>
+      <c r="T216" t="inlineStr"/>
+      <c r="U216" t="inlineStr"/>
+      <c r="V216" t="inlineStr"/>
+      <c r="W216" t="inlineStr"/>
+      <c r="X216" t="inlineStr"/>
+      <c r="Y216" t="inlineStr"/>
+      <c r="Z216" t="inlineStr"/>
+      <c r="AA216" t="inlineStr"/>
+      <c r="AB216" t="inlineStr"/>
+      <c r="AC216" t="inlineStr"/>
+      <c r="AD216" t="inlineStr"/>
+      <c r="AE216" t="inlineStr"/>
+      <c r="AF216" t="inlineStr"/>
+      <c r="AG216" t="inlineStr"/>
+      <c r="AH216" t="inlineStr"/>
+      <c r="AI216" t="inlineStr"/>
+      <c r="AJ216" t="inlineStr"/>
+      <c r="AK216" t="inlineStr"/>
+      <c r="AL216" t="inlineStr"/>
+      <c r="AM216" t="inlineStr"/>
+      <c r="AN216" t="inlineStr"/>
+      <c r="AO216" t="inlineStr"/>
+      <c r="AP216" t="inlineStr"/>
+      <c r="AQ216" t="inlineStr"/>
+      <c r="AR216" t="inlineStr"/>
+      <c r="AS216" t="inlineStr"/>
+      <c r="AT216" t="inlineStr"/>
+      <c r="AU216" t="inlineStr"/>
+      <c r="AV216" t="inlineStr"/>
+      <c r="AW216" t="inlineStr"/>
+      <c r="AX216" t="inlineStr"/>
+      <c r="AY216" t="inlineStr"/>
+      <c r="AZ216" t="inlineStr"/>
+      <c r="BA216" t="inlineStr"/>
+      <c r="BB216" t="inlineStr"/>
+      <c r="BC216" t="inlineStr"/>
+      <c r="BD216" t="inlineStr"/>
+      <c r="BE216" t="inlineStr"/>
+      <c r="BF216" t="inlineStr"/>
+      <c r="BG216" t="inlineStr"/>
+      <c r="BH216" t="inlineStr"/>
+      <c r="BI216" t="inlineStr"/>
+      <c r="BJ216" t="inlineStr"/>
+      <c r="BK216" t="inlineStr"/>
+      <c r="BL216" t="inlineStr"/>
+      <c r="BM216" t="inlineStr"/>
+      <c r="BN216" t="inlineStr"/>
+      <c r="BO216" t="inlineStr"/>
+      <c r="BP216" t="inlineStr"/>
+      <c r="BQ216" t="inlineStr"/>
+      <c r="BR216" t="inlineStr"/>
+      <c r="BS216" t="inlineStr"/>
+      <c r="BT216" t="inlineStr"/>
+      <c r="BU216" t="inlineStr"/>
+      <c r="BV216" t="inlineStr"/>
+      <c r="BW216" t="inlineStr"/>
+      <c r="BX216" t="inlineStr"/>
+      <c r="BY216" t="inlineStr"/>
+      <c r="BZ216" t="inlineStr"/>
+      <c r="CA216" t="inlineStr"/>
+      <c r="CB216" t="inlineStr"/>
+      <c r="CC216" t="inlineStr"/>
+      <c r="CD216" t="inlineStr"/>
+      <c r="CE216" t="inlineStr"/>
+      <c r="CF216" t="inlineStr"/>
+      <c r="CG216" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gafor_log.xlsx
+++ b/data/gafor_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CG216"/>
+  <dimension ref="A1:CG217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29008,6 +29008,137 @@
       <c r="CF216" t="inlineStr"/>
       <c r="CG216" t="inlineStr"/>
     </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2026-10-30 08:00</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Ostfriesland</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Nordfriesland-Dithmarschen</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Schleswig-Holsteinische Geest</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>Schleswig-Holsteinisches Hügelland</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>Nordwestliches Niedersachsen</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>Lüneburger Heide</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>Westliches Niedersachsen</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>Hannover und Braunschweig</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>Teutoburger Wald</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Weser-Leine-Bergland</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr"/>
+      <c r="M217" t="inlineStr"/>
+      <c r="N217" t="inlineStr"/>
+      <c r="O217" t="inlineStr"/>
+      <c r="P217" t="inlineStr"/>
+      <c r="Q217" t="inlineStr"/>
+      <c r="R217" t="inlineStr"/>
+      <c r="S217" t="inlineStr"/>
+      <c r="T217" t="inlineStr"/>
+      <c r="U217" t="inlineStr"/>
+      <c r="V217" t="inlineStr"/>
+      <c r="W217" t="inlineStr"/>
+      <c r="X217" t="inlineStr"/>
+      <c r="Y217" t="inlineStr"/>
+      <c r="Z217" t="inlineStr"/>
+      <c r="AA217" t="inlineStr"/>
+      <c r="AB217" t="inlineStr"/>
+      <c r="AC217" t="inlineStr"/>
+      <c r="AD217" t="inlineStr"/>
+      <c r="AE217" t="inlineStr"/>
+      <c r="AF217" t="inlineStr"/>
+      <c r="AG217" t="inlineStr"/>
+      <c r="AH217" t="inlineStr"/>
+      <c r="AI217" t="inlineStr"/>
+      <c r="AJ217" t="inlineStr"/>
+      <c r="AK217" t="inlineStr"/>
+      <c r="AL217" t="inlineStr"/>
+      <c r="AM217" t="inlineStr"/>
+      <c r="AN217" t="inlineStr"/>
+      <c r="AO217" t="inlineStr"/>
+      <c r="AP217" t="inlineStr"/>
+      <c r="AQ217" t="inlineStr"/>
+      <c r="AR217" t="inlineStr"/>
+      <c r="AS217" t="inlineStr"/>
+      <c r="AT217" t="inlineStr"/>
+      <c r="AU217" t="inlineStr"/>
+      <c r="AV217" t="inlineStr"/>
+      <c r="AW217" t="inlineStr"/>
+      <c r="AX217" t="inlineStr"/>
+      <c r="AY217" t="inlineStr"/>
+      <c r="AZ217" t="inlineStr"/>
+      <c r="BA217" t="inlineStr"/>
+      <c r="BB217" t="inlineStr"/>
+      <c r="BC217" t="inlineStr"/>
+      <c r="BD217" t="inlineStr"/>
+      <c r="BE217" t="inlineStr"/>
+      <c r="BF217" t="inlineStr"/>
+      <c r="BG217" t="inlineStr"/>
+      <c r="BH217" t="inlineStr"/>
+      <c r="BI217" t="inlineStr"/>
+      <c r="BJ217" t="inlineStr"/>
+      <c r="BK217" t="inlineStr"/>
+      <c r="BL217" t="inlineStr"/>
+      <c r="BM217" t="inlineStr"/>
+      <c r="BN217" t="inlineStr"/>
+      <c r="BO217" t="inlineStr"/>
+      <c r="BP217" t="inlineStr"/>
+      <c r="BQ217" t="inlineStr"/>
+      <c r="BR217" t="inlineStr"/>
+      <c r="BS217" t="inlineStr"/>
+      <c r="BT217" t="inlineStr"/>
+      <c r="BU217" t="inlineStr"/>
+      <c r="BV217" t="inlineStr"/>
+      <c r="BW217" t="inlineStr"/>
+      <c r="BX217" t="inlineStr"/>
+      <c r="BY217" t="inlineStr"/>
+      <c r="BZ217" t="inlineStr"/>
+      <c r="CA217" t="inlineStr"/>
+      <c r="CB217" t="inlineStr"/>
+      <c r="CC217" t="inlineStr"/>
+      <c r="CD217" t="inlineStr"/>
+      <c r="CE217" t="inlineStr"/>
+      <c r="CF217" t="inlineStr"/>
+      <c r="CG217" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/gafor_log.xlsx
+++ b/data/gafor_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CG217"/>
+  <dimension ref="A1:CG218"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29139,6 +29139,137 @@
       <c r="CF217" t="inlineStr"/>
       <c r="CG217" t="inlineStr"/>
     </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2026-10-31 08:00</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Ostfriesland</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Nordfriesland-Dithmarschen</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Schleswig-Holsteinische Geest</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>Schleswig-Holsteinisches Hügelland</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>Nordwestliches Niedersachsen</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>Lüneburger Heide</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>Westliches Niedersachsen</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>Hannover und Braunschweig</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>Teutoburger Wald</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Weser-Leine-Bergland</t>
+        </is>
+      </c>
+      <c r="L218" t="inlineStr"/>
+      <c r="M218" t="inlineStr"/>
+      <c r="N218" t="inlineStr"/>
+      <c r="O218" t="inlineStr"/>
+      <c r="P218" t="inlineStr"/>
+      <c r="Q218" t="inlineStr"/>
+      <c r="R218" t="inlineStr"/>
+      <c r="S218" t="inlineStr"/>
+      <c r="T218" t="inlineStr"/>
+      <c r="U218" t="inlineStr"/>
+      <c r="V218" t="inlineStr"/>
+      <c r="W218" t="inlineStr"/>
+      <c r="X218" t="inlineStr"/>
+      <c r="Y218" t="inlineStr"/>
+      <c r="Z218" t="inlineStr"/>
+      <c r="AA218" t="inlineStr"/>
+      <c r="AB218" t="inlineStr"/>
+      <c r="AC218" t="inlineStr"/>
+      <c r="AD218" t="inlineStr"/>
+      <c r="AE218" t="inlineStr"/>
+      <c r="AF218" t="inlineStr"/>
+      <c r="AG218" t="inlineStr"/>
+      <c r="AH218" t="inlineStr"/>
+      <c r="AI218" t="inlineStr"/>
+      <c r="AJ218" t="inlineStr"/>
+      <c r="AK218" t="inlineStr"/>
+      <c r="AL218" t="inlineStr"/>
+      <c r="AM218" t="inlineStr"/>
+      <c r="AN218" t="inlineStr"/>
+      <c r="AO218" t="inlineStr"/>
+      <c r="AP218" t="inlineStr"/>
+      <c r="AQ218" t="inlineStr"/>
+      <c r="AR218" t="inlineStr"/>
+      <c r="AS218" t="inlineStr"/>
+      <c r="AT218" t="inlineStr"/>
+      <c r="AU218" t="inlineStr"/>
+      <c r="AV218" t="inlineStr"/>
+      <c r="AW218" t="inlineStr"/>
+      <c r="AX218" t="inlineStr"/>
+      <c r="AY218" t="inlineStr"/>
+      <c r="AZ218" t="inlineStr"/>
+      <c r="BA218" t="inlineStr"/>
+      <c r="BB218" t="inlineStr"/>
+      <c r="BC218" t="inlineStr"/>
+      <c r="BD218" t="inlineStr"/>
+      <c r="BE218" t="inlineStr"/>
+      <c r="BF218" t="inlineStr"/>
+      <c r="BG218" t="inlineStr"/>
+      <c r="BH218" t="inlineStr"/>
+      <c r="BI218" t="inlineStr"/>
+      <c r="BJ218" t="inlineStr"/>
+      <c r="BK218" t="inlineStr"/>
+      <c r="BL218" t="inlineStr"/>
+      <c r="BM218" t="inlineStr"/>
+      <c r="BN218" t="inlineStr"/>
+      <c r="BO218" t="inlineStr"/>
+      <c r="BP218" t="inlineStr"/>
+      <c r="BQ218" t="inlineStr"/>
+      <c r="BR218" t="inlineStr"/>
+      <c r="BS218" t="inlineStr"/>
+      <c r="BT218" t="inlineStr"/>
+      <c r="BU218" t="inlineStr"/>
+      <c r="BV218" t="inlineStr"/>
+      <c r="BW218" t="inlineStr"/>
+      <c r="BX218" t="inlineStr"/>
+      <c r="BY218" t="inlineStr"/>
+      <c r="BZ218" t="inlineStr"/>
+      <c r="CA218" t="inlineStr"/>
+      <c r="CB218" t="inlineStr"/>
+      <c r="CC218" t="inlineStr"/>
+      <c r="CD218" t="inlineStr"/>
+      <c r="CE218" t="inlineStr"/>
+      <c r="CF218" t="inlineStr"/>
+      <c r="CG218" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
